--- a/output/full_scan/batch_seq3_2026-10-08.xlsx
+++ b/output/full_scan/batch_seq3_2026-10-08.xlsx
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>76.45534887181469</v>
+        <v>76.45534892006495</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>29.16214163532953</v>
+        <v>29.1621416387618</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1.53634927716005</v>
@@ -570,7 +570,7 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.1271192943152057</v>
+        <v>0.1271192942622303</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>61.45756348720222</v>
+        <v>61.45756353027819</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>11.17216313129728</v>
+        <v>11.17216333149276</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>1.647711687838602</v>
@@ -623,7 +623,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1141888970493327</v>
+        <v>0.1141888968712947</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>63.11306701643399</v>
+        <v>63.11306699265009</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>16.19297190143281</v>
+        <v>16.19297184277554</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>5.058008947146207</v>
@@ -676,7 +676,7 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.0178334152635899</v>
+        <v>0.0178334152524633</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>63.08702132915892</v>
+        <v>63.0870213297239</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>30.33196654159895</v>
+        <v>30.33196654985727</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>1.419707879810233</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>70.81944672403056</v>
+        <v>70.81944679625229</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>26.42949805275513</v>
+        <v>26.42949806210782</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>2.967716570204979</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1.561420738442969</v>
+        <v>1.561420738331697</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>69.35993883521843</v>
+        <v>69.35993884233798</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>26.36444201045214</v>
+        <v>26.3644419648098</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>2.402820677695992</v>
@@ -835,7 +835,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1.799429338650644</v>
+        <v>1.799429338684028</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>67.70096580743643</v>
+        <v>67.70096581390698</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>18.77185563048449</v>
+        <v>18.77185563663852</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>6.478128287332894</v>
@@ -888,7 +888,7 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.6833642595304834</v>
+        <v>0.6833642595193602</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>68.87562337011673</v>
+        <v>68.87562334555099</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>41.07101413244116</v>
+        <v>41.07101413442446</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>0.6847643170286102</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.0519830159869316</v>
+        <v>0.0519830160203174</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>63.94352015758012</v>
+        <v>63.9435201830793</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>19.62842376296237</v>
+        <v>19.62842380362466</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>2.108941271811392</v>
@@ -994,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.7282228351349134</v>
+        <v>0.7282228350236472</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>922.8264666569791</v>
+        <v>922.8264666569788</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1270</v>
@@ -1029,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>66.79485249248674</v>
+        <v>66.7948525059887</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>28.31248975910962</v>
+        <v>28.31248980419486</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>0.5863127058136999</v>
@@ -1047,7 +1047,7 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>21.01379009588412</v>
+        <v>21.01379009532783</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>71.72778276659311</v>
+        <v>71.72778285067352</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>20.59401847492343</v>
+        <v>20.59401848212228</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>1.576950395112557</v>
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>5.947212058404113</v>
+        <v>5.947212059183052</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>912.231418113428</v>
+        <v>912.2314181134284</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>132.5</v>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>68.28194791383302</v>
+        <v>68.28194806733917</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>16.50688573921553</v>
+        <v>16.50688575603381</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>1.092602826241415</v>
@@ -1153,7 +1153,7 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.8181839484296881</v>
+        <v>0.8181839480068545</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>911.764201332365</v>
+        <v>911.7642013323648</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>145</v>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>61.35605802573196</v>
+        <v>61.35605797573869</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>41.23786997167935</v>
+        <v>41.23786997544398</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>1.105450608621021</v>
@@ -1206,7 +1206,7 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.8084442016681654</v>
+        <v>0.8084442013343449</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>61.52550000237139</v>
+        <v>61.52550002961303</v>
       </c>
       <c r="I15" s="2" t="n">
         <v>24.13261711204913</v>
@@ -1259,7 +1259,7 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.1597830863423368</v>
+        <v>0.1597830861197948</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>61.42922037194655</v>
+        <v>61.42922034142718</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>34.56571950862094</v>
+        <v>34.56571950862092</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>0.6944967244618357</v>
@@ -1312,7 +1312,7 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.2346081753214628</v>
+        <v>-0.2346081753325852</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>73.27553036753314</v>
+        <v>73.27553041667846</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>34.44475897290796</v>
+        <v>34.44475898117826</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>0.6825701563009359</v>
@@ -1365,7 +1365,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>4.437624590634883</v>
+        <v>4.437624590189852</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>60.35458677268478</v>
+        <v>60.35458671640266</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>14.99952692833705</v>
+        <v>14.99952694978566</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>0.6176122664364789</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>872.0574540776837</v>
+        <v>872.0574540776836</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>36.7</v>
@@ -1453,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>55.31952640238544</v>
+        <v>55.31952639820381</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>25.19117938908097</v>
+        <v>25.19117940918392</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>0.5188841340719633</v>
@@ -1471,7 +1471,7 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.0694868455392684</v>
+        <v>-0.0694868455058836</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>855.0656982986843</v>
+        <v>855.0656982986844</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>31.95</v>
@@ -1509,7 +1509,7 @@
         <v>61.12753459245248</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>13.42756609347958</v>
+        <v>13.42756609179199</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>2.102745068766554</v>
@@ -1524,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.1031327679346593</v>
+        <v>0.1031327678790205</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>72.88192270838383</v>
+        <v>72.88192271007424</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>27.01562458712673</v>
+        <v>27.01562461800257</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>1.760175335808465</v>
@@ -1598,7 +1598,7 @@
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>849.8905604598654</v>
+        <v>849.8905604598656</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>243.5</v>
@@ -1612,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>63.37291582784276</v>
+        <v>63.37291582079134</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>18.2712218983996</v>
+        <v>18.27122190716159</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>2.146463650550482</v>
@@ -1630,7 +1630,7 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>4.47035671558702</v>
+        <v>4.470356715475746</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>59.00102333725381</v>
+        <v>59.00102340123653</v>
       </c>
       <c r="I23" s="2" t="n">
         <v>31.95087708911255</v>
@@ -1683,7 +1683,7 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.5257799253808979</v>
+        <v>0.5257799248245436</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>847.618856841792</v>
+        <v>847.6188568417917</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>51.1</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>66.02313585716325</v>
+        <v>66.02313587369517</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>32.47064672119332</v>
+        <v>32.47064672169719</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>0.8333525372244619</v>
@@ -1736,7 +1736,7 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.400129948732093</v>
+        <v>0.4001299487765979</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1771,10 +1771,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>63.27757662110346</v>
+        <v>63.27757663603444</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>13.3710183944447</v>
+        <v>13.37101840094512</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>2.045917044638552</v>
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>2.064003469842835</v>
+        <v>2.064003469954109</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>795.8332716711187</v>
+        <v>795.8332716711186</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>33.2</v>
@@ -1824,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>72.22443418779764</v>
+        <v>72.2244341571747</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>41.98048415151429</v>
+        <v>41.98048401241482</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>1.111026684245253</v>
@@ -1842,7 +1842,7 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.4983237030901877</v>
+        <v>0.4983237033794963</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>784.6374117157632</v>
+        <v>784.6374117157633</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>211</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>58.33273941582098</v>
+        <v>58.33273941804636</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>25.8710961302575</v>
+        <v>25.87109614515093</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>0.6246121104413546</v>
@@ -1895,7 +1895,7 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>1.449324198958303</v>
+        <v>1.449324199002813</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>56.49551524747484</v>
+        <v>56.49551513523384</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>25.8309666305065</v>
+        <v>25.83096659228407</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>1.527461685522735</v>
@@ -1948,7 +1948,7 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.0615283690832701</v>
+        <v>-0.0615283690721443</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1983,10 +1983,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>64.03400984943194</v>
+        <v>64.03400990407863</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>46.01775391004334</v>
+        <v>46.01775434778837</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>0.6720627160835494</v>
@@ -2001,7 +2001,7 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.1273621908652843</v>
+        <v>-0.127362190976549</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>67.21106884094033</v>
+        <v>67.21106886393511</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>33.66669988695637</v>
+        <v>33.66669991460707</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>0.5839557732674189</v>
@@ -2054,7 +2054,7 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>6.898875169641101</v>
+        <v>6.898875169463025</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2089,10 +2089,10 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>56.38366706797917</v>
+        <v>56.38366707822837</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>16.3682190830648</v>
+        <v>16.36821905525412</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>0.914308699200523</v>
@@ -2107,7 +2107,7 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>12.03322890514284</v>
+        <v>12.03322889957926</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>50.78621354144086</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>24.57482445680239</v>
+        <v>24.57482450022761</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>0.2528069540021731</v>
@@ -2160,7 +2160,7 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.1482020979490615</v>
+        <v>-0.1482020978934249</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>57.30004824217204</v>
+        <v>57.30004811205699</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>23.44193476658004</v>
+        <v>23.44193486415746</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>0.7122291921512059</v>
@@ -2213,7 +2213,7 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.0474424444394844</v>
+        <v>0.047442445329675</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2248,10 +2248,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>64.88934777767638</v>
+        <v>64.88934775944949</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>52.52018632588455</v>
+        <v>52.52018634436224</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>0.6153529734989762</v>
@@ -2266,7 +2266,7 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.1231690370282745</v>
+        <v>0.1231690370839106</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>51.96578841618619</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>31.07698098278086</v>
+        <v>31.07698103340855</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>0.5626819817271111</v>
@@ -2319,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.6278223206288924</v>
+        <v>-0.6278223203618376</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>60.25683573180509</v>
+        <v>60.25683567276156</v>
       </c>
       <c r="I36" s="2" t="n">
         <v>30.25480365996508</v>
@@ -2372,7 +2372,7 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.2820180517268826</v>
+        <v>-0.2820180516156223</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2407,10 +2407,10 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>64.57407790501333</v>
+        <v>64.57407792825794</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>33.78006368413533</v>
+        <v>33.78006372074815</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>0.8194751485443865</v>
@@ -2425,7 +2425,7 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.223434622431693</v>
+        <v>-0.2234346222091539</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>751.6818192002208</v>
+        <v>751.6818192002207</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>16.3</v>
@@ -2460,10 +2460,10 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>53.92214608162076</v>
+        <v>53.92214607657421</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>6.216463590128178</v>
+        <v>6.216463590128181</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>4.743981953586107</v>
@@ -2478,7 +2478,7 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.2416517147200285</v>
+        <v>0.2416517147422827</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>748.9955927303745</v>
+        <v>748.9955927303752</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>329</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>58.07186454676617</v>
+        <v>58.07186457018228</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>14.95834053308669</v>
+        <v>14.95834055680261</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>0.9078362733231808</v>
@@ -2531,7 +2531,7 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.9442352147387952</v>
+        <v>0.94423521507265</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2566,10 +2566,10 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>57.09918306941487</v>
+        <v>57.09918306339342</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>35.76718942086236</v>
+        <v>35.76718944311072</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>0.7508867942452564</v>
@@ -2584,7 +2584,7 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-4.216053622234028</v>
+        <v>-4.216053622345299</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>59.68173788405321</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>39.04824416016047</v>
+        <v>39.04824402926882</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>3.448151378147453</v>
@@ -2637,7 +2637,7 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.03402947496679</v>
+        <v>-0.0340294750886562</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>719.0372240421692</v>
+        <v>719.0372240421656</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>39.6</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>58.96383454780655</v>
+        <v>58.96383424413432</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>22.4643413785205</v>
+        <v>22.46434156372451</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>1.287948019005943</v>
@@ -2690,7 +2690,7 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.1147454287908931</v>
+        <v>0.1147454298591009</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2725,10 +2725,10 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>60.88509776808827</v>
+        <v>60.88509776140627</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>25.48232428395442</v>
+        <v>25.48232430374589</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>0.7966177658776836</v>
@@ -2743,7 +2743,7 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.9107502303882776</v>
+        <v>0.9107502304550376</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>56.21725881702937</v>
+        <v>56.21725882529236</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>30.03465444907633</v>
+        <v>30.03465451256099</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>0.6925067586592338</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.6690205458041856</v>
+        <v>0.6690205454703566</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>66.47723741564269</v>
+        <v>66.47723744081132</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>21.61304020879133</v>
+        <v>21.61304023503783</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>0.7524466240010222</v>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>55.60695900473195</v>
+        <v>55.60695905468042</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>33.84212773884666</v>
+        <v>33.84212775844003</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>0.4559214057120711</v>
@@ -2902,7 +2902,7 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.0952465901358667</v>
+        <v>-0.0952465899578385</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2937,10 +2937,10 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>59.25842358031752</v>
+        <v>59.25842368620811</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>38.79650075549955</v>
+        <v>38.79650101072402</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>0.6893646682283873</v>
@@ -2955,7 +2955,7 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.1826639001354162</v>
+        <v>-0.1826639002021812</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>670.956022044082</v>
+        <v>670.9560220440825</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>130.5</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>63.98540180105817</v>
+        <v>63.98540187076158</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>16.98741149240651</v>
+        <v>16.98741149964235</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>2.276313149637385</v>
@@ -3008,7 +3008,7 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>1.043963756412584</v>
+        <v>1.04396375676865</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>647.2187920121625</v>
+        <v>647.2187920121627</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>216.5</v>
@@ -3043,10 +3043,10 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>63.1443790176059</v>
+        <v>63.14437905363093</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>15.55322336522135</v>
+        <v>15.55322343603116</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>0.9823894969014648</v>
@@ -3061,7 +3061,7 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>3.48735511509712</v>
+        <v>3.487355115653499</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3096,10 +3096,10 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>54.23827406293509</v>
+        <v>54.23827392978807</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>8.781240240188874</v>
+        <v>8.781239478105814</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>0.6675488898691369</v>
@@ -3114,7 +3114,7 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>2.629762639639482</v>
+        <v>2.629762658511098</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>50.70458203820132</v>
+        <v>50.70458207331546</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>28.42789278726312</v>
+        <v>28.42789273968878</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>0.4376343808176557</v>
@@ -3167,7 +3167,7 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.4596418393098296</v>
+        <v>-0.4596418389092556</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>639.6408840965782</v>
+        <v>639.6408840965781</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>63.6</v>
@@ -3202,10 +3202,10 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>51.50443657997326</v>
+        <v>51.50443659673014</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>10.4749645385343</v>
+        <v>10.4749647384877</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>0.7675686211542143</v>
@@ -3220,7 +3220,7 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.3552548972660641</v>
+        <v>0.3552548971436553</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>639.1678096745986</v>
+        <v>639.1678096745985</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>44.05</v>
@@ -3255,10 +3255,10 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>52.76036905595211</v>
+        <v>52.76036906127862</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>33.37423523673525</v>
+        <v>33.37423521151685</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>0.8439268367929332</v>
@@ -3273,7 +3273,7 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.2305657974860311</v>
+        <v>-0.2305657975305357</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>638.4999580082606</v>
+        <v>638.4999580082607</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>16.5</v>
@@ -3308,7 +3308,7 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>52.66368257013787</v>
+        <v>52.66368241848235</v>
       </c>
       <c r="I54" s="2" t="n">
         <v>22.30760423913329</v>
@@ -3326,7 +3326,7 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.0866190578672998</v>
+        <v>-0.0866190578116634</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3361,10 +3361,10 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>65.71814017620818</v>
+        <v>65.7181403162937</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>36.52184587049582</v>
+        <v>36.52184586778987</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>0.8636811282878285</v>
@@ -3379,7 +3379,7 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.1419440126120073</v>
+        <v>0.1419440125341176</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>62.18279283012708</v>
+        <v>62.18279280892308</v>
       </c>
       <c r="I56" s="2" t="n">
         <v>21.04682989897179</v>
@@ -3432,7 +3432,7 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.1283581594123962</v>
+        <v>0.1283581594457782</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>52.49015289166384</v>
+        <v>52.49015288331909</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>42.59393308142992</v>
+        <v>42.59393308142994</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>0.531455843295538</v>
@@ -3485,7 +3485,7 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.2045367275199276</v>
+        <v>-0.2045367276089487</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>615.3305473806753</v>
+        <v>615.3305473806754</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>2960</v>
@@ -3520,10 +3520,10 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>54.02700755872203</v>
+        <v>54.02700756127351</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>17.65162028775201</v>
+        <v>17.65162022409574</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>0.889601139185641</v>
@@ -3538,7 +3538,7 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>19.13578221610493</v>
+        <v>19.13578222489537</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3573,10 +3573,10 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>53.1429125148392</v>
+        <v>53.14291228986846</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>28.62678465021892</v>
+        <v>28.62678462001572</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>0.4611427244367433</v>
@@ -3591,7 +3591,7 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.2683288478843227</v>
+        <v>-0.2683288473724715</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>48.2211877078817</v>
+        <v>48.2211878070498</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>24.37208588278826</v>
+        <v>24.3720858523328</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>1.067285085815881</v>
@@ -3644,7 +3644,7 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.1919259047172124</v>
+        <v>-0.191925904828486</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>56.14069446121045</v>
+        <v>56.14069446478128</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>13.04859926932389</v>
+        <v>13.04859927420394</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>1.061168667670709</v>
@@ -3697,7 +3697,7 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>1.651382714859918</v>
+        <v>1.651382714837662</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3732,10 +3732,10 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>58.82554064364514</v>
+        <v>58.82554064883829</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>28.77032972958915</v>
+        <v>28.77032973246373</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>0.967609636205357</v>
@@ -3771,7 +3771,7 @@
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>598.2574879512075</v>
+        <v>598.2574879512081</v>
       </c>
       <c r="E63" s="2" t="n">
         <v>110</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>50.1868683449929</v>
+        <v>50.18686832784376</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>29.28233427559815</v>
+        <v>29.28233426508717</v>
       </c>
       <c r="J63" s="2" t="n">
         <v>1.023974108576607</v>
@@ -3803,7 +3803,7 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.4566453184019698</v>
+        <v>-0.4566453183797132</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3838,10 +3838,10 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>56.07975463292978</v>
+        <v>56.07975472647512</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>41.91303020211642</v>
+        <v>41.913030130303</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>0.4363882427902917</v>
@@ -3856,7 +3856,7 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.3606801602303771</v>
+        <v>-0.3606801603416452</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>56.25511828149197</v>
+        <v>56.25511834169224</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>13.86048707736209</v>
+        <v>13.86048725861465</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>0.9037483184595756</v>
@@ -3909,7 +3909,7 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.1260534628446032</v>
+        <v>-0.1260534630893974</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>69.31235161401165</v>
+        <v>69.31235169656915</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>32.67098318611523</v>
+        <v>32.67098321330322</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>0.8525799405593154</v>
@@ -3962,7 +3962,7 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.397920989902933</v>
+        <v>0.3979209898584258</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -3997,10 +3997,10 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>55.55560280534378</v>
+        <v>55.55560286677306</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>32.52683947937824</v>
+        <v>32.52683954094918</v>
       </c>
       <c r="J67" s="2" t="n">
         <v>0.6854242224348428</v>
@@ -4015,7 +4015,7 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.2044810984344558</v>
+        <v>-0.2044810985012163</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>46.82487033186595</v>
+        <v>46.82487025531729</v>
       </c>
       <c r="I68" s="2" t="n">
         <v>28.58866373026174</v>
@@ -4068,7 +4068,7 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.8369335146560477</v>
+        <v>-0.8369335145447707</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>568.22099975316</v>
+        <v>568.2209997531598</v>
       </c>
       <c r="E69" s="2" t="n">
         <v>46.55</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>48.69071655041296</v>
+        <v>48.69071672000568</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>28.33669887630432</v>
+        <v>28.33669885331103</v>
       </c>
       <c r="J69" s="2" t="n">
         <v>0.6492018873071583</v>
@@ -4121,7 +4121,7 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.4266774039644734</v>
+        <v>0.4266774039422216</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
@@ -4156,10 +4156,10 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>57.65298548697887</v>
+        <v>57.65298554471153</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>47.56093776053952</v>
+        <v>47.56093780887974</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>0.6315761955833161</v>
@@ -4174,7 +4174,7 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.009861305634868801</v>
+        <v>-0.009861305701631601</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>563.4544735510582</v>
+        <v>563.4544735510581</v>
       </c>
       <c r="E71" s="2" t="n">
         <v>531</v>
@@ -4209,10 +4209,10 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>45.16496355112098</v>
+        <v>45.1649635475215</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>18.67712482735552</v>
+        <v>18.67712484965302</v>
       </c>
       <c r="J71" s="2" t="n">
         <v>0.7580300074202138</v>
@@ -4227,7 +4227,7 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-2.636711938967085</v>
+        <v>-2.636711940079839</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>559.4806213669556</v>
+        <v>559.4806213669548</v>
       </c>
       <c r="E72" s="2" t="n">
         <v>8.32</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>58.01215307954994</v>
+        <v>58.01215314964218</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>16.68274987716014</v>
+        <v>16.68274979982523</v>
       </c>
       <c r="J72" s="2" t="n">
         <v>1.350879938526235</v>
@@ -4280,7 +4280,7 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.0205504881967954</v>
+        <v>0.0205504884193373</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4315,10 +4315,10 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>49.47909167987654</v>
+        <v>49.47909182421807</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>23.61550930138042</v>
+        <v>23.61550933230466</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>0.1649987747043492</v>
@@ -4333,7 +4333,7 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.1550921959184987</v>
+        <v>-0.1550921960965358</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>551.929289288722</v>
+        <v>551.9292892887221</v>
       </c>
       <c r="E74" s="2" t="n">
         <v>213</v>
@@ -4368,10 +4368,10 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>43.39584981891772</v>
+        <v>43.39584993742227</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>26.8518359252364</v>
+        <v>26.85183594063328</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>1.171202038746936</v>
@@ -4386,7 +4386,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.1915649330182343</v>
+        <v>0.1915649326844182</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>54.04827646871245</v>
+        <v>54.04827648349145</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>22.57927265695776</v>
+        <v>22.57927269773167</v>
       </c>
       <c r="J75" s="2" t="n">
         <v>0.6736633893150124</v>
@@ -4439,7 +4439,7 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.2471984298556608</v>
+        <v>-0.2471984299446809</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4474,10 +4474,10 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>48.90451800826634</v>
+        <v>48.90451808955988</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>32.61397803113755</v>
+        <v>32.61397809504865</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>0.2268951679351208</v>
@@ -4492,7 +4492,7 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.6584512698586886</v>
+        <v>-0.6584512700812311</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>534.629299415975</v>
+        <v>534.6292994159749</v>
       </c>
       <c r="E77" s="2" t="n">
         <v>552</v>
@@ -4527,10 +4527,10 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>49.43286511425533</v>
+        <v>49.43286512910748</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>12.53280241355525</v>
+        <v>12.53280242240897</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>1.014056338082817</v>
@@ -4545,7 +4545,7 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>3.654110181103688</v>
+        <v>3.654110180992446</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>534.3432243343547</v>
+        <v>534.3432243343548</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>185</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>59.98350038050334</v>
+        <v>59.98350034915309</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>16.95207098582516</v>
+        <v>16.95207107285232</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>1.156518303598061</v>
@@ -4598,7 +4598,7 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.6060473074698822</v>
+        <v>0.6060473080262613</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>534.0986164937975</v>
+        <v>534.0986164937976</v>
       </c>
       <c r="E79" s="2" t="n">
         <v>58.1</v>
@@ -4633,10 +4633,10 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>52.90719893292145</v>
+        <v>52.90719881547128</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>24.56568223155239</v>
+        <v>24.56568197014727</v>
       </c>
       <c r="J79" s="2" t="n">
         <v>0.4327829851595053</v>
@@ -4651,7 +4651,7 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.0733340066872048</v>
+        <v>-0.073334006420155</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4686,10 +4686,10 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>53.81515957794787</v>
+        <v>53.81515959084311</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>13.84047181701109</v>
+        <v>13.84047182844354</v>
       </c>
       <c r="J80" s="2" t="n">
         <v>1.062039272868343</v>
@@ -4704,7 +4704,7 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.0565367063146212</v>
+        <v>0.0565367064258879</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>50.88169660986809</v>
+        <v>50.88169667101549</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>20.72468758501534</v>
+        <v>20.72468759373304</v>
       </c>
       <c r="J81" s="2" t="n">
         <v>1.87377663670574</v>
@@ -4757,7 +4757,7 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.457250573260866</v>
+        <v>0.4572505732386115</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>513.9087616867898</v>
+        <v>513.9087616867891</v>
       </c>
       <c r="E82" s="2" t="n">
         <v>19.1</v>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>56.30674927612579</v>
+        <v>56.30674929973411</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>24.89221605592829</v>
+        <v>24.89221609846834</v>
       </c>
       <c r="J82" s="2" t="n">
         <v>0.8994667110400992</v>
@@ -4810,7 +4810,7 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.1305014638991155</v>
+        <v>0.1305014639213682</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -4845,10 +4845,10 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>53.79751675211804</v>
+        <v>53.7975167718915</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>22.89439942013397</v>
+        <v>22.89439942013398</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>0.7268901292355514</v>
@@ -4863,7 +4863,7 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.6661421163664443</v>
+        <v>0.6661421161884311</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>505.9959151295865</v>
+        <v>505.995915129586</v>
       </c>
       <c r="E84" s="2" t="n">
         <v>22</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>49.25396663601128</v>
+        <v>49.25396667915797</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>19.41545010485057</v>
+        <v>19.41545018963921</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>1.01635673563096</v>
@@ -4916,7 +4916,7 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.0141926797911089</v>
+        <v>-0.0141926798356154</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>51.71062103012032</v>
+        <v>51.71062072464703</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>35.21966015648312</v>
+        <v>35.21966023274503</v>
       </c>
       <c r="J85" s="2" t="n">
         <v>0.8098892878360918</v>
@@ -4969,7 +4969,7 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.0773989637245333</v>
+        <v>-0.07739896359100989</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -5004,10 +5004,10 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>47.8349225599835</v>
+        <v>47.83492261916096</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>23.50421383077583</v>
+        <v>23.50421389900548</v>
       </c>
       <c r="J86" s="2" t="n">
         <v>0.6618224938727191</v>
@@ -5022,7 +5022,7 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.3793035895522945</v>
+        <v>0.3793035891517287</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>52.84512464841027</v>
+        <v>52.84512469167135</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>14.60166796619226</v>
+        <v>14.60166798283247</v>
       </c>
       <c r="J87" s="2" t="n">
         <v>1.059466512407928</v>
@@ -5075,7 +5075,7 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-7.8066202077095</v>
+        <v>-7.80662020882265</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -5110,10 +5110,10 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>47.4995191350832</v>
+        <v>47.49951923961035</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>20.79875280506576</v>
+        <v>20.79875287813569</v>
       </c>
       <c r="J88" s="2" t="n">
         <v>0.6016354168252437</v>
@@ -5128,7 +5128,7 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.0270356985368958</v>
+        <v>0.0270356985146418</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5163,10 +5163,10 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>53.32100349069285</v>
+        <v>53.32100332391303</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>21.17683123923614</v>
+        <v>21.17683131202534</v>
       </c>
       <c r="J89" s="2" t="n">
         <v>0.761545814045633</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.07070335189546879</v>
+        <v>0.0707033521180138</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>59.21489929237948</v>
+        <v>59.21489929404957</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>32.27098593719891</v>
+        <v>32.27098590008472</v>
       </c>
       <c r="J90" s="2" t="n">
         <v>0.6386354321177182</v>
@@ -5234,7 +5234,7 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.8986595641430748</v>
+        <v>0.8986595641653339</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>43.58110166912807</v>
+        <v>43.58110168746114</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>7.016155804121212</v>
+        <v>7.016155832342461</v>
       </c>
       <c r="J91" s="2" t="n">
         <v>0.9947913848930594</v>
@@ -5287,7 +5287,7 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.4844201295772721</v>
+        <v>0.484420131802695</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -5322,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>55.47644699442658</v>
+        <v>55.47644705009844</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>34.96734186274094</v>
+        <v>34.9673418078572</v>
       </c>
       <c r="J92" s="2" t="n">
         <v>0.6096156755113674</v>
@@ -5340,7 +5340,7 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.2763031647553158</v>
+        <v>-0.2763031648220774</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>55.41207372950178</v>
+        <v>55.4120738165611</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>9.205580403607996</v>
+        <v>9.205580455792774</v>
       </c>
       <c r="J93" s="2" t="n">
         <v>1.144478073142968</v>
@@ -5414,7 +5414,7 @@
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>490.8616951017067</v>
+        <v>490.8616951017066</v>
       </c>
       <c r="E94" s="2" t="n">
         <v>12.1</v>
@@ -5428,10 +5428,10 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>52.45909485070233</v>
+        <v>52.45909449784181</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>7.647882204658058</v>
+        <v>7.64788225775673</v>
       </c>
       <c r="J94" s="2" t="n">
         <v>0.9271753708803868</v>
@@ -5446,7 +5446,7 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.2731912463112484</v>
+        <v>0.2731912464525083</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>62.17757164715938</v>
+        <v>62.17757162792974</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>46.95835327059336</v>
+        <v>46.9583532367068</v>
       </c>
       <c r="J95" s="2" t="n">
         <v>0.3792163408687066</v>
@@ -5499,7 +5499,7 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.1820624277119333</v>
+        <v>0.1820624277453124</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>53.09614053919375</v>
+        <v>53.09614056169681</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>16.65716169399778</v>
+        <v>16.65716169399779</v>
       </c>
       <c r="J96" s="2" t="n">
         <v>0.8926934694292411</v>
@@ -5587,10 +5587,10 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>47.02380357122719</v>
+        <v>47.02380359601796</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>16.71361783808661</v>
+        <v>16.71361786633378</v>
       </c>
       <c r="J97" s="2" t="n">
         <v>0.8231411506543366</v>
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.2756009162576108</v>
+        <v>-0.2756009163354905</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5640,10 +5640,10 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>48.51666643138637</v>
+        <v>48.5166664226841</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>18.7995998354041</v>
+        <v>18.79959981856109</v>
       </c>
       <c r="J98" s="2" t="n">
         <v>0.5248180736331473</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.9747594306751812</v>
+        <v>-0.9747594299185294</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>476.9348369979483</v>
+        <v>476.9348369979484</v>
       </c>
       <c r="E99" s="2" t="n">
         <v>137</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>48.36679700843144</v>
+        <v>48.36679689408254</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>17.18457790804525</v>
+        <v>17.18457785630737</v>
       </c>
       <c r="J99" s="2" t="n">
         <v>0.5804712086609459</v>
@@ -5711,7 +5711,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.2416704561506577</v>
+        <v>0.241670457040814</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>464.8719609262192</v>
+        <v>464.871960926219</v>
       </c>
       <c r="E100" s="2" t="n">
         <v>11.95</v>
@@ -5749,7 +5749,7 @@
         <v>49.549328837681</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>20.1241827221354</v>
+        <v>20.12418272213539</v>
       </c>
       <c r="J100" s="2" t="n">
         <v>0.945037886320406</v>
@@ -5764,7 +5764,7 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.0170971758910466</v>
+        <v>0.0170971759133008</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -5799,10 +5799,10 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>49.00324703990645</v>
+        <v>49.00324704263437</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>8.379429658115399</v>
+        <v>8.379429745527119</v>
       </c>
       <c r="J101" s="2" t="n">
         <v>1.396623157661756</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.1082144260539092</v>
+        <v>0.1082144257868788</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>59.34090284951682</v>
+        <v>59.34090288611333</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>23.5515654802678</v>
+        <v>23.55156548513825</v>
       </c>
       <c r="J102" s="2" t="n">
         <v>0.5475450310343187</v>
@@ -5870,7 +5870,7 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.3141820199003048</v>
+        <v>0.3141820199559424</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>460.2301268785112</v>
+        <v>460.230126878512</v>
       </c>
       <c r="E103" s="2" t="n">
         <v>56.2</v>
@@ -5905,7 +5905,7 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>55.92685398146306</v>
+        <v>55.92685399479157</v>
       </c>
       <c r="I103" s="2" t="n">
         <v>34.78583659979661</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.7852548994277182</v>
+        <v>0.7852548994054619</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5958,10 +5958,10 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>49.6468611681585</v>
+        <v>49.64686119396449</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>31.93821401945262</v>
+        <v>31.93821396706442</v>
       </c>
       <c r="J104" s="2" t="n">
         <v>1.121352560833478</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-50.06003076192724</v>
+        <v>-50.06003076637901</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>56.17518418978889</v>
+        <v>56.17518422716645</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>36.26868204907036</v>
+        <v>36.2686820528824</v>
       </c>
       <c r="J105" s="2" t="n">
         <v>0.5723853576086476</v>
@@ -6064,10 +6064,10 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>53.21460330823599</v>
+        <v>53.21460337175024</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>23.57428874068441</v>
+        <v>23.57428876650814</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>0.4652025587143022</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.06409968227800369</v>
+        <v>0.0640996819886995</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>52.85388230921383</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>35.7838424265968</v>
+        <v>35.78384243656978</v>
       </c>
       <c r="J107" s="2" t="n">
         <v>0.9766990117950652</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.4102932750941299</v>
+        <v>-0.4102932750830088</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>452.7422065098373</v>
+        <v>452.7422065098374</v>
       </c>
       <c r="E108" s="2" t="n">
         <v>41</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>48.50003849386263</v>
+        <v>48.50003851209726</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>28.65576086283999</v>
+        <v>28.65576091124708</v>
       </c>
       <c r="J108" s="2" t="n">
         <v>0.9151723080650735</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.4318290604198262</v>
+        <v>-0.4318290604532093</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6223,10 +6223,10 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>52.49301205569976</v>
+        <v>52.49301226413851</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>14.7130703270773</v>
+        <v>14.7130706178152</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>1.783247408392926</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0015300804194261</v>
+        <v>0.0015300803415326</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>451.785477180759</v>
+        <v>451.7854771807596</v>
       </c>
       <c r="E110" s="2" t="n">
         <v>42</v>
@@ -6276,10 +6276,10 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>54.10668566616364</v>
+        <v>54.10668570577177</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>28.37564123842289</v>
+        <v>28.3756413108493</v>
       </c>
       <c r="J110" s="2" t="n">
         <v>0.4580482600235035</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.101902454233136</v>
+        <v>0.1019024551789341</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>65.35183643223519</v>
+        <v>65.35183659691418</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>10.95146366012487</v>
+        <v>10.95146370675128</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>1.86080786961663</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.1409453066461522</v>
+        <v>0.1409453064903727</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>55.60466914185658</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>21.16544055887091</v>
+        <v>21.16544057927067</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>0.827162336283781</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.142252071684817</v>
+        <v>0.1422520715067775</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6435,10 +6435,10 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>42.9053465907724</v>
+        <v>42.90534648227435</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>19.90857077175496</v>
+        <v>19.90857070935625</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>0.2162505386362421</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>1.762254127637974e-05</v>
+        <v>1.762253460053931e-05</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>46.18152190122498</v>
+        <v>46.18152187132195</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>26.44753585299404</v>
+        <v>26.44753587146588</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>1.309942484930338</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.0169778021456306</v>
+        <v>-0.0169778021233701</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>424.5889441014739</v>
+        <v>424.5889441014741</v>
       </c>
       <c r="E115" s="2" t="n">
         <v>14.35</v>
@@ -6541,10 +6541,10 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>51.64164768709411</v>
+        <v>51.64164770042345</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>25.76107183825846</v>
+        <v>25.76107191306012</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>0.3692636336874076</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.0116000560287932</v>
+        <v>0.0116000561511921</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6594,10 +6594,10 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>42.94084510141452</v>
+        <v>42.94084512247801</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>23.22641770867099</v>
+        <v>23.22641773482401</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>0.4919888552491568</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.0367572093181871</v>
+        <v>-0.0367572093111242</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>417.4818300723597</v>
+        <v>417.4818300723596</v>
       </c>
       <c r="E117" s="2" t="n">
         <v>10.7</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>46.01555724322701</v>
+        <v>46.01555722433625</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>29.12462772022234</v>
+        <v>29.12462772780846</v>
       </c>
       <c r="J117" s="2" t="n">
         <v>0.4955901261101565</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.0744722432333414</v>
+        <v>-0.0744722432355666</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6700,10 +6700,10 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>54.76611160906837</v>
+        <v>54.76611144943276</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>28.7956955695605</v>
+        <v>28.79569561113157</v>
       </c>
       <c r="J118" s="2" t="n">
         <v>0.4948861319153823</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.0401146724234185</v>
+        <v>0.0401146725569412</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
@@ -6753,10 +6753,10 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>40.63013238499976</v>
+        <v>40.63013242993419</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>18.77808525155888</v>
+        <v>18.77808525515146</v>
       </c>
       <c r="J119" s="2" t="n">
         <v>1.552911778057812</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.6090891880292412</v>
+        <v>-0.6090891880069942</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>44.16480980724639</v>
+        <v>44.16480981978086</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>28.50889415362479</v>
+        <v>28.50889422658356</v>
       </c>
       <c r="J120" s="2" t="n">
         <v>0.8730358830063155</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.7681943951930497</v>
+        <v>0.7681943949704977</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6859,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>46.09465740925136</v>
+        <v>46.09465741862643</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>14.85180709453793</v>
+        <v>14.85180711183099</v>
       </c>
       <c r="J121" s="2" t="n">
         <v>0.9013174907501434</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-1.53869887799567</v>
+        <v>-1.538698878218225</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         <v>46.52478853033107</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>20.6924890896474</v>
+        <v>20.69248907956834</v>
       </c>
       <c r="J122" s="2" t="n">
         <v>0.791986819447853</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>47.10699731299035</v>
+        <v>47.10699735776388</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>24.4515333218066</v>
+        <v>24.45153331661906</v>
       </c>
       <c r="J123" s="2" t="n">
         <v>0.5056415748598001</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.1015499448518061</v>
+        <v>-0.1015499448851869</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -7018,10 +7018,10 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>49.2528331895631</v>
+        <v>49.25283321809001</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>19.86471323492724</v>
+        <v>19.86471323857404</v>
       </c>
       <c r="J124" s="2" t="n">
         <v>0.2881659334399506</v>
@@ -7071,10 +7071,10 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>31.63601087743652</v>
+        <v>31.63601090960995</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>31.41020819633899</v>
+        <v>31.4102081648634</v>
       </c>
       <c r="J125" s="2" t="n">
         <v>0.5751414246013501</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.4081675022815973</v>
+        <v>-0.408167502270476</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>47.87462812351742</v>
+        <v>47.87462814855186</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>23.17534125293977</v>
+        <v>23.17534125293978</v>
       </c>
       <c r="J126" s="2" t="n">
         <v>0.2002691929731018</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.1169331920565005</v>
+        <v>-0.1169331920676274</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7177,10 +7177,10 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>46.84474530978731</v>
+        <v>46.84474533701404</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>18.27934078533905</v>
+        <v>18.27934077422409</v>
       </c>
       <c r="J127" s="2" t="n">
         <v>0.6901614062294043</v>
@@ -7216,7 +7216,7 @@
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>376.5904118949338</v>
+        <v>376.5904118949337</v>
       </c>
       <c r="E128" s="2" t="n">
         <v>16.85</v>
@@ -7230,10 +7230,10 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>47.85978777219087</v>
+        <v>47.85978791132083</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>20.30129305333283</v>
+        <v>20.30129310536552</v>
       </c>
       <c r="J128" s="2" t="n">
         <v>0.3364516421504003</v>
@@ -7248,7 +7248,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-0.0645042578892962</v>
+        <v>-0.064504257922676</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>376.3299980343434</v>
+        <v>376.3299980343433</v>
       </c>
       <c r="E129" s="2" t="n">
         <v>10.45</v>
@@ -7283,10 +7283,10 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>45.44046101792483</v>
+        <v>45.44046114886734</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>25.76074720899966</v>
+        <v>25.7607471319477</v>
       </c>
       <c r="J129" s="2" t="n">
         <v>0.5175032938158998</v>
@@ -7301,7 +7301,7 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>0.0315021139499495</v>
+        <v>0.0315021139610777</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>374.9417959317134</v>
+        <v>374.9417959317135</v>
       </c>
       <c r="E130" s="2" t="n">
         <v>22</v>
@@ -7336,10 +7336,10 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>46.99881796246606</v>
+        <v>46.99881774070453</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>20.046011564163</v>
+        <v>20.04601166265961</v>
       </c>
       <c r="J130" s="2" t="n">
         <v>1.243893123940176</v>
@@ -7354,7 +7354,7 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>-0.0490579158639588</v>
+        <v>-0.0490579157081774</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
@@ -7389,10 +7389,10 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>49.64988842792402</v>
+        <v>49.64988845581865</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>23.94359146307684</v>
+        <v>23.94359157621871</v>
       </c>
       <c r="J131" s="2" t="n">
         <v>0.5719317913122453</v>
@@ -7407,7 +7407,7 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>-1.096542335051811</v>
+        <v>-1.096542335296628</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>369.0623839731143</v>
+        <v>369.4950536815604</v>
       </c>
       <c r="E132" s="2" t="n">
         <v>56.6</v>
@@ -7442,7 +7442,7 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>41.2368269443129</v>
+        <v>47.27338050924554</v>
       </c>
       <c r="I132" s="2" t="n">
         <v/>
@@ -7460,7 +7460,7 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>0.07556675925052669</v>
+        <v>0.0647090202583521</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
@@ -7495,10 +7495,10 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>45.70441322509145</v>
+        <v>45.70441340927634</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>23.57900649031991</v>
+        <v>23.57900654020676</v>
       </c>
       <c r="J133" s="2" t="n">
         <v>0.5318095837324148</v>
@@ -7513,7 +7513,7 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>-0.0014496627201508</v>
+        <v>-0.0014496627535413</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>0</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>45.27994709226099</v>
+        <v>45.2799471041786</v>
       </c>
       <c r="I134" s="2" t="n">
         <v>9.584815559577134</v>
@@ -7566,7 +7566,7 @@
         <v>-1</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>-0.0624611080785685</v>
+        <v>-0.0624611080563216</v>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
@@ -7601,10 +7601,10 @@
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>44.74711929575707</v>
+        <v>44.74711933266114</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>10.21486245555527</v>
+        <v>10.21486251442942</v>
       </c>
       <c r="J135" s="2" t="n">
         <v>0.1464165753032451</v>
@@ -7619,7 +7619,7 @@
         <v>-1</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>-0.0640593145323769</v>
+        <v>-0.064059314643648</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
@@ -7654,10 +7654,10 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>48.74593354193559</v>
+        <v>48.74593356028227</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>16.33093593888945</v>
+        <v>16.33093596990988</v>
       </c>
       <c r="J136" s="2" t="n">
         <v>0.6545179807884831</v>
@@ -7672,7 +7672,7 @@
         <v>-1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>0.0974923118747632</v>
+        <v>0.09749231169672901</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
@@ -7707,10 +7707,10 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>49.26404663423109</v>
+        <v>49.264046643117</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>10.07539446353701</v>
+        <v>10.07539446390502</v>
       </c>
       <c r="J137" s="2" t="n">
         <v>0.4974322078050959</v>
@@ -7746,7 +7746,7 @@
         <v/>
       </c>
       <c r="D138" s="2" t="n">
-        <v>351.0301550990767</v>
+        <v>351.0301550990766</v>
       </c>
       <c r="E138" s="2" t="n">
         <v>20.1</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>41.27101712217246</v>
+        <v>41.27101716752522</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>13.13542612569872</v>
+        <v>13.13542611792548</v>
       </c>
       <c r="J138" s="2" t="n">
         <v>0.6748515247649027</v>
@@ -7778,7 +7778,7 @@
         <v>-1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>0.0109770068582522</v>
+        <v>0.010977006836002</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
@@ -7813,10 +7813,10 @@
         <v>0</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>45.82778750661704</v>
+        <v>45.82778747752892</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>19.92889084302988</v>
+        <v>19.92889072873198</v>
       </c>
       <c r="J139" s="2" t="n">
         <v>0.5790078569279881</v>
@@ -7831,7 +7831,7 @@
         <v>-1</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>-0.0552716327629713</v>
+        <v>-0.0552716326695025</v>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v/>
       </c>
       <c r="D140" s="2" t="n">
-        <v>345.5520037969903</v>
+        <v>345.5520037969901</v>
       </c>
       <c r="E140" s="2" t="n">
         <v>267</v>
@@ -7866,10 +7866,10 @@
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>44.8795950229305</v>
+        <v>44.87959502059068</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>15.40809707975424</v>
+        <v>15.4080971478286</v>
       </c>
       <c r="J140" s="2" t="n">
         <v>0.6052563069198605</v>
@@ -7884,7 +7884,7 @@
         <v>-1</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>-2.889025477962703</v>
+        <v>-2.88902547794044</v>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         <v>0</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>50.10933020613354</v>
+        <v>50.10933025308419</v>
       </c>
       <c r="I141" s="2" t="n">
         <v>28.42871866090482</v>
@@ -7937,7 +7937,7 @@
         <v>-1</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>0.0252017607796355</v>
+        <v>0.0252017607462529</v>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v/>
       </c>
       <c r="D142" s="2" t="n">
-        <v>337.5286951206242</v>
+        <v>337.5286951206259</v>
       </c>
       <c r="E142" s="2" t="n">
         <v>12.1</v>
@@ -7972,10 +7972,10 @@
         <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>33.45362558491478</v>
+        <v>33.4536256264615</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>28.65141199707157</v>
+        <v>28.65141202372292</v>
       </c>
       <c r="J142" s="2" t="n">
         <v>1.053047595234831</v>
@@ -8011,7 +8011,7 @@
         <v/>
       </c>
       <c r="D143" s="2" t="n">
-        <v>337.4215190603519</v>
+        <v>337.4215190603497</v>
       </c>
       <c r="E143" s="2" t="n">
         <v>18.75</v>
@@ -8025,10 +8025,10 @@
         <v>0</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>53.41203550324931</v>
+        <v>53.41203561687751</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>32.90322170218361</v>
+        <v>32.90322169167846</v>
       </c>
       <c r="J143" s="2" t="n">
         <v>0.3527219224086896</v>
@@ -8043,7 +8043,7 @@
         <v>-1</v>
       </c>
       <c r="N143" s="2" t="n">
-        <v>-0.0392894815796227</v>
+        <v>-0.0392894813793341</v>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
@@ -8078,10 +8078,10 @@
         <v>0</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>37.92353755523548</v>
+        <v>37.92353760001554</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>13.73664482830318</v>
+        <v>13.73664498515738</v>
       </c>
       <c r="J144" s="2" t="n">
         <v>0.6365377550577058</v>
@@ -8096,7 +8096,7 @@
         <v>-1</v>
       </c>
       <c r="N144" s="2" t="n">
-        <v>0.1748890029657374</v>
+        <v>0.1748890027320677</v>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v/>
       </c>
       <c r="D145" s="2" t="n">
-        <v>330.4135262659161</v>
+        <v>330.4135262659152</v>
       </c>
       <c r="E145" s="2" t="n">
         <v>15.6</v>
@@ -8131,10 +8131,10 @@
         <v>0</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>43.35201255673594</v>
+        <v>43.35201262673599</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>25.0743916222624</v>
+        <v>25.07439165391062</v>
       </c>
       <c r="J145" s="2" t="n">
         <v>1.063786777092382</v>
@@ -8149,7 +8149,7 @@
         <v>-1</v>
       </c>
       <c r="N145" s="2" t="n">
-        <v>-0.086724041082769</v>
+        <v>-0.0867240411357398</v>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
@@ -8184,10 +8184,10 @@
         <v>0</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>53.90377219489035</v>
+        <v>53.90377220189234</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>24.59669889258228</v>
+        <v>24.59669890955134</v>
       </c>
       <c r="J146" s="2" t="n">
         <v>0.2749650480660545</v>
@@ -8202,7 +8202,7 @@
         <v>-1</v>
       </c>
       <c r="N146" s="2" t="n">
-        <v>0.1989056850975454</v>
+        <v>0.198905685075289</v>
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>44.94649968203738</v>
+        <v>44.94649975044322</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>20.91348415074121</v>
+        <v>20.91348416530726</v>
       </c>
       <c r="J147" s="2" t="n">
         <v>0.8450869927082509</v>
@@ -8255,7 +8255,7 @@
         <v>-1</v>
       </c>
       <c r="N147" s="2" t="n">
-        <v>-0.2968914472941186</v>
+        <v>-0.2968914473386272</v>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
@@ -8290,10 +8290,10 @@
         <v>0</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>50.46904830905836</v>
+        <v>50.46904839299133</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>16.19861506265902</v>
+        <v>16.19861502252649</v>
       </c>
       <c r="J148" s="2" t="n">
         <v>0.8113257395164939</v>
@@ -8308,7 +8308,7 @@
         <v>-1</v>
       </c>
       <c r="N148" s="2" t="n">
-        <v>-0.0156889233838193</v>
+        <v>-0.0156889234172058</v>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
@@ -8343,10 +8343,10 @@
         <v>0</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>50.55498029641596</v>
+        <v>50.55498048003523</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>17.91736231667629</v>
+        <v>17.91736238238053</v>
       </c>
       <c r="J149" s="2" t="n">
         <v>0.7170181032339032</v>
@@ -8361,7 +8361,7 @@
         <v>-1</v>
       </c>
       <c r="N149" s="2" t="n">
-        <v>0.008681071232558599</v>
+        <v>0.0086810712103045</v>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v/>
       </c>
       <c r="D150" s="2" t="n">
-        <v>318.0515893145173</v>
+        <v>318.0515893145183</v>
       </c>
       <c r="E150" s="2" t="n">
         <v>20.55</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>47.77533803301365</v>
+        <v>47.77533817284539</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>8.373727060588475</v>
+        <v>8.373727145370323</v>
       </c>
       <c r="J150" s="2" t="n">
         <v>0.7006248934929467</v>
@@ -8414,7 +8414,7 @@
         <v>-1</v>
       </c>
       <c r="N150" s="2" t="n">
-        <v>0.0368724135365016</v>
+        <v>0.036872413458611</v>
       </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
@@ -8449,10 +8449,10 @@
         <v>0</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>43.19834769983381</v>
+        <v>43.19834772361923</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>11.46690336452313</v>
+        <v>11.46690331991395</v>
       </c>
       <c r="J151" s="2" t="n">
         <v>0.3635667759315786</v>
@@ -8488,7 +8488,7 @@
         <v/>
       </c>
       <c r="D152" s="2" t="n">
-        <v>308.6131081855577</v>
+        <v>308.6131081855573</v>
       </c>
       <c r="E152" s="2" t="n">
         <v>38.1</v>
@@ -8502,10 +8502,10 @@
         <v>0</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>45.18819206231429</v>
+        <v>45.18819183547164</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>17.3569624015946</v>
+        <v>17.35696265334143</v>
       </c>
       <c r="J152" s="2" t="n">
         <v>0.7332246997543435</v>
@@ -8520,7 +8520,7 @@
         <v>-1</v>
       </c>
       <c r="N152" s="2" t="n">
-        <v>0.1320164222473649</v>
+        <v>0.1320164226479434</v>
       </c>
       <c r="O152" s="2" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         <v/>
       </c>
       <c r="D153" s="2" t="n">
-        <v>307.6159440582487</v>
+        <v>307.6159440582486</v>
       </c>
       <c r="E153" s="2" t="n">
         <v>120.5</v>
@@ -8555,10 +8555,10 @@
         <v>0</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>50.52108804767821</v>
+        <v>50.52108796203723</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>17.09636784635859</v>
+        <v>17.09636786901175</v>
       </c>
       <c r="J153" s="2" t="n">
         <v>0.3994530956789767</v>
@@ -8573,7 +8573,7 @@
         <v>-1</v>
       </c>
       <c r="N153" s="2" t="n">
-        <v>0.688668353870862</v>
+        <v>0.688668354204685</v>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v/>
       </c>
       <c r="D154" s="2" t="n">
-        <v>302.0873783281724</v>
+        <v>302.0873783281725</v>
       </c>
       <c r="E154" s="2" t="n">
         <v>46.15</v>
@@ -8608,10 +8608,10 @@
         <v>0</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>51.8411330345534</v>
+        <v>51.84113304400449</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>17.22070856551878</v>
+        <v>17.22070858492274</v>
       </c>
       <c r="J154" s="2" t="n">
         <v>0.6534980418214584</v>
@@ -8626,7 +8626,7 @@
         <v>-1</v>
       </c>
       <c r="N154" s="2" t="n">
-        <v>0.3648375153245904</v>
+        <v>0.3648375152578256</v>
       </c>
       <c r="O154" s="2" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>-1</v>
       </c>
       <c r="N155" s="2" t="n">
-        <v>0.0389564606627074</v>
+        <v>0.0389564606404527</v>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v/>
       </c>
       <c r="D156" s="2" t="n">
-        <v>298.156294697386</v>
+        <v>298.1562946973851</v>
       </c>
       <c r="E156" s="2" t="n">
         <v>5.76</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>50.37029240567247</v>
+        <v>50.37029246629105</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>13.54600163042434</v>
+        <v>13.54600164110626</v>
       </c>
       <c r="J156" s="2" t="n">
         <v>0.4260448494178075</v>
@@ -8732,7 +8732,7 @@
         <v>-1</v>
       </c>
       <c r="N156" s="2" t="n">
-        <v>-0.0100050990731664</v>
+        <v>-0.0100050991020968</v>
       </c>
       <c r="O156" s="2" t="inlineStr">
         <is>
@@ -8767,10 +8767,10 @@
         <v>0</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>31.84176574276633</v>
+        <v>31.8417656794298</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>17.97810274236556</v>
+        <v>17.97810273748159</v>
       </c>
       <c r="J157" s="2" t="n">
         <v>0.9243291834187418</v>
@@ -8785,7 +8785,7 @@
         <v>-1</v>
       </c>
       <c r="N157" s="2" t="n">
-        <v>-1.430265852178211</v>
+        <v>-1.430265852289448</v>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>35.78232882068748</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>9.855236293557631</v>
+        <v>9.855236322187489</v>
       </c>
       <c r="J158" s="2" t="n">
         <v>1.049942804899381</v>
@@ -8838,7 +8838,7 @@
         <v>-1</v>
       </c>
       <c r="N158" s="2" t="n">
-        <v>0.0229671210376349</v>
+        <v>0.0229671210153838</v>
       </c>
       <c r="O158" s="2" t="inlineStr">
         <is>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>36.32244639961661</v>
+        <v>36.3224466875572</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>28.77270575249434</v>
+        <v>28.77270565898539</v>
       </c>
       <c r="J159" s="2" t="n">
         <v>1.149047968989999</v>
@@ -8891,7 +8891,7 @@
         <v>-1</v>
       </c>
       <c r="N159" s="2" t="n">
-        <v>0.0329935992114156</v>
+        <v>0.032993599289312</v>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v/>
       </c>
       <c r="D160" s="2" t="n">
-        <v>287.7919663318523</v>
+        <v>287.7919663318524</v>
       </c>
       <c r="E160" s="2" t="n">
         <v>51.7</v>
@@ -8926,10 +8926,10 @@
         <v>0</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>41.04974443295783</v>
+        <v>41.04974446622001</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>16.92916597336697</v>
+        <v>16.92916595429906</v>
       </c>
       <c r="J160" s="2" t="n">
         <v>0.9659409054300599</v>
@@ -8944,7 +8944,7 @@
         <v>-1</v>
       </c>
       <c r="N160" s="2" t="n">
-        <v>0.0289227827850392</v>
+        <v>0.0289227826515099</v>
       </c>
       <c r="O160" s="2" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         <v/>
       </c>
       <c r="D161" s="2" t="n">
-        <v>286.1689742295587</v>
+        <v>286.1689742295588</v>
       </c>
       <c r="E161" s="2" t="n">
         <v>21.5</v>
@@ -8979,10 +8979,10 @@
         <v>0</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>51.75171770755108</v>
+        <v>51.7517176577799</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>17.36521809628947</v>
+        <v>17.36521807215324</v>
       </c>
       <c r="J161" s="2" t="n">
         <v>0.4183082172547885</v>
@@ -8997,7 +8997,7 @@
         <v>-1</v>
       </c>
       <c r="N161" s="2" t="n">
-        <v>0.0616364284399794</v>
+        <v>0.0616364284177239</v>
       </c>
       <c r="O161" s="2" t="inlineStr">
         <is>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>22.46845413825787</v>
+        <v>22.46845405141066</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>30.80158409495755</v>
+        <v>30.80158401380417</v>
       </c>
       <c r="J162" s="2" t="n">
         <v>0.7421047831587415</v>
@@ -9050,7 +9050,7 @@
         <v>-1</v>
       </c>
       <c r="N162" s="2" t="n">
-        <v>-0.3411836213861202</v>
+        <v>-0.3411836212859775</v>
       </c>
       <c r="O162" s="2" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         <v/>
       </c>
       <c r="D163" s="2" t="n">
-        <v>282.6913520346993</v>
+        <v>282.6913520346985</v>
       </c>
       <c r="E163" s="2" t="n">
         <v>38.9</v>
@@ -9088,7 +9088,7 @@
         <v>52.06862570831957</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>16.19468910159201</v>
+        <v>16.19468911364697</v>
       </c>
       <c r="J163" s="2" t="n">
         <v>0.3904601636818935</v>
@@ -9103,7 +9103,7 @@
         <v>-1</v>
       </c>
       <c r="N163" s="2" t="n">
-        <v>-0.0064389870727811</v>
+        <v>-0.0064389871172897</v>
       </c>
       <c r="O163" s="2" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
         <v>0</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>40.18550137958267</v>
+        <v>40.18550134570779</v>
       </c>
       <c r="I164" s="2" t="n">
         <v>13.39657598634548</v>
@@ -9156,7 +9156,7 @@
         <v>-1</v>
       </c>
       <c r="N164" s="2" t="n">
-        <v>0.1101323291130971</v>
+        <v>0.1101323291353502</v>
       </c>
       <c r="O164" s="2" t="inlineStr">
         <is>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>51.40524779620397</v>
+        <v>51.40524781900758</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>20.62536604638439</v>
+        <v>20.62536602029079</v>
       </c>
       <c r="J165" s="2" t="n">
         <v>0.4625664133366969</v>
@@ -9209,7 +9209,7 @@
         <v>-1</v>
       </c>
       <c r="N165" s="2" t="n">
-        <v>0.0620453154291185</v>
+        <v>0.0620453154068664</v>
       </c>
       <c r="O165" s="2" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v/>
       </c>
       <c r="D166" s="2" t="n">
-        <v>281.9725361765376</v>
+        <v>281.9725361765377</v>
       </c>
       <c r="E166" s="2" t="n">
         <v>11.6</v>
@@ -9244,10 +9244,10 @@
         <v>0</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>51.82604975672089</v>
+        <v>51.82604970848711</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>18.970745984813</v>
+        <v>18.97074597603515</v>
       </c>
       <c r="J166" s="2" t="n">
         <v>0.659036611911667</v>
@@ -9262,7 +9262,7 @@
         <v>-1</v>
       </c>
       <c r="N166" s="2" t="n">
-        <v>0.0163652027783233</v>
+        <v>0.0163652028117058</v>
       </c>
       <c r="O166" s="2" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>0</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>46.11181634598277</v>
+        <v>46.11181643778363</v>
       </c>
       <c r="I167" s="2" t="n">
         <v>7.989331142245902</v>
@@ -9315,7 +9315,7 @@
         <v>-1</v>
       </c>
       <c r="N167" s="2" t="n">
-        <v>0.0130193772742788</v>
+        <v>0.0130193772520277</v>
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>45.0858091620915</v>
+        <v>45.08580910514147</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>11.62788293651854</v>
+        <v>11.62788302064551</v>
       </c>
       <c r="J168" s="2" t="n">
         <v>0.7580132154298453</v>
@@ -9368,7 +9368,7 @@
         <v>-1</v>
       </c>
       <c r="N168" s="2" t="n">
-        <v>0.0655522116583528</v>
+        <v>0.0655522117362419</v>
       </c>
       <c r="O168" s="2" t="inlineStr">
         <is>
@@ -9403,10 +9403,10 @@
         <v>0</v>
       </c>
       <c r="H169" s="2" t="n">
-        <v>36.67479942003914</v>
+        <v>36.67479935113923</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>10.93404827927074</v>
+        <v>10.93404828734326</v>
       </c>
       <c r="J169" s="2" t="n">
         <v>2.885710891427134</v>
@@ -9456,10 +9456,10 @@
         <v>0</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>51.58697742527365</v>
+        <v>51.58697723314374</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>28.2245227267789</v>
+        <v>28.22452296314442</v>
       </c>
       <c r="J170" s="2" t="n">
         <v>0.584491119334033</v>
@@ -9474,7 +9474,7 @@
         <v>-1</v>
       </c>
       <c r="N170" s="2" t="n">
-        <v>-0.043600668059177</v>
+        <v>-0.0436006678143792</v>
       </c>
       <c r="O170" s="2" t="inlineStr">
         <is>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>44.47912277102423</v>
+        <v>44.47912264063589</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>19.30496157911108</v>
+        <v>19.30496152274933</v>
       </c>
       <c r="J171" s="2" t="n">
         <v>0.2700469796999978</v>
@@ -9527,7 +9527,7 @@
         <v>-1</v>
       </c>
       <c r="N171" s="2" t="n">
-        <v>-0.1529997779420351</v>
+        <v>-0.1529997778864005</v>
       </c>
       <c r="O171" s="2" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v/>
       </c>
       <c r="D172" s="2" t="n">
-        <v>259.0340509264767</v>
+        <v>259.0340509264766</v>
       </c>
       <c r="E172" s="2" t="n">
         <v>155</v>
@@ -9562,10 +9562,10 @@
         <v>0</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>45.86299091341429</v>
+        <v>45.86299085927416</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>17.54829531508419</v>
+        <v>17.54829545648398</v>
       </c>
       <c r="J172" s="2" t="n">
         <v>0.2852960787354688</v>
@@ -9580,7 +9580,7 @@
         <v>-1</v>
       </c>
       <c r="N172" s="2" t="n">
-        <v>-0.8557519727143578</v>
+        <v>-0.8557519723805236</v>
       </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
@@ -9615,10 +9615,10 @@
         <v>0</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>34.77894214317712</v>
+        <v>34.77894208731342</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>20.06164398013495</v>
+        <v>20.06164401361689</v>
       </c>
       <c r="J173" s="2" t="n">
         <v>0.2668711513159156</v>
@@ -9633,7 +9633,7 @@
         <v>-1</v>
       </c>
       <c r="N173" s="2" t="n">
-        <v>-0.0512474129799844</v>
+        <v>-0.0512474128019485</v>
       </c>
       <c r="O173" s="2" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>0</v>
       </c>
       <c r="H174" s="2" t="n">
-        <v>48.11205679134989</v>
+        <v>48.11205697165254</v>
       </c>
       <c r="I174" s="2" t="n">
         <v>23.78975874929501</v>
@@ -9686,7 +9686,7 @@
         <v>-1</v>
       </c>
       <c r="N174" s="2" t="n">
-        <v>-0.1347734925790182</v>
+        <v>-0.1347734926680349</v>
       </c>
       <c r="O174" s="2" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v/>
       </c>
       <c r="D175" s="2" t="n">
-        <v>255.6791549455289</v>
+        <v>255.6791549455241</v>
       </c>
       <c r="E175" s="2" t="n">
         <v>77</v>
@@ -9721,10 +9721,10 @@
         <v>0</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>47.02759118544699</v>
+        <v>47.02759165555731</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>18.91524809935918</v>
+        <v>18.91524798590038</v>
       </c>
       <c r="J175" s="2" t="n">
         <v>0.3943189530515097</v>
@@ -9739,7 +9739,7 @@
         <v>-1</v>
       </c>
       <c r="N175" s="2" t="n">
-        <v>0.1092732772046025</v>
+        <v>0.1092732748678958</v>
       </c>
       <c r="O175" s="2" t="inlineStr">
         <is>
@@ -9774,10 +9774,10 @@
         <v>0</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>44.32115323882638</v>
+        <v>44.32115330028908</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>9.928065424522464</v>
+        <v>9.928065437020054</v>
       </c>
       <c r="J176" s="2" t="n">
         <v>1.010905389554014</v>
@@ -9792,7 +9792,7 @@
         <v>-1</v>
       </c>
       <c r="N176" s="2" t="n">
-        <v>-0.0231343794941864</v>
+        <v>-0.0231343795053133</v>
       </c>
       <c r="O176" s="2" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>0</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>45.16735946481138</v>
+        <v>45.16735938424264</v>
       </c>
       <c r="I177" s="2" t="n">
         <v>22.37044857349421</v>
@@ -9866,7 +9866,7 @@
         <v/>
       </c>
       <c r="D178" s="2" t="n">
-        <v>246.8076686467846</v>
+        <v>246.8076686467858</v>
       </c>
       <c r="E178" s="2" t="n">
         <v>13.75</v>
@@ -9880,10 +9880,10 @@
         <v>0</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>44.7274628192799</v>
+        <v>44.72746286048744</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>11.93196274286533</v>
+        <v>11.93196269953143</v>
       </c>
       <c r="J178" s="2" t="n">
         <v>0.9274814593020974</v>
@@ -9898,7 +9898,7 @@
         <v>-1</v>
       </c>
       <c r="N178" s="2" t="n">
-        <v>-0.0317870008375646</v>
+        <v>-0.0317870008820729</v>
       </c>
       <c r="O178" s="2" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>0</v>
       </c>
       <c r="H179" s="2" t="n">
-        <v>41.43662986168404</v>
+        <v>41.43662977078607</v>
       </c>
       <c r="I179" s="2" t="n">
         <v>14.30774757701548</v>
@@ -9951,7 +9951,7 @@
         <v>-1</v>
       </c>
       <c r="N179" s="2" t="n">
-        <v>-0.010608954864477</v>
+        <v>-0.0106089548533502</v>
       </c>
       <c r="O179" s="2" t="inlineStr">
         <is>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="H180" s="2" t="n">
-        <v>45.05189753027888</v>
+        <v>45.05189765417538</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>30.41767967803171</v>
+        <v>30.41767979284721</v>
       </c>
       <c r="J180" s="2" t="n">
         <v>0.5297246999504828</v>
@@ -10025,7 +10025,7 @@
         <v/>
       </c>
       <c r="D181" s="2" t="n">
-        <v>238.5236147712394</v>
+        <v>238.5236147712393</v>
       </c>
       <c r="E181" s="2" t="n">
         <v>44.15</v>
@@ -10039,10 +10039,10 @@
         <v>0</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>47.07459552326076</v>
+        <v>47.07459582592374</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>14.90476590210319</v>
+        <v>14.90476592823938</v>
       </c>
       <c r="J181" s="2" t="n">
         <v>0.8528506316383421</v>
@@ -10057,7 +10057,7 @@
         <v>-1</v>
       </c>
       <c r="N181" s="2" t="n">
-        <v>0.2582819934197169</v>
+        <v>0.2582819935198598</v>
       </c>
       <c r="O181" s="2" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v/>
       </c>
       <c r="D182" s="2" t="n">
-        <v>235.2771319143468</v>
+        <v>235.2771319143467</v>
       </c>
       <c r="E182" s="2" t="n">
         <v>176</v>
@@ -10092,10 +10092,10 @@
         <v>0</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>45.24615448635636</v>
+        <v>45.24615443665581</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>17.31208698467769</v>
+        <v>17.31208707706766</v>
       </c>
       <c r="J182" s="2" t="n">
         <v>1.290423063201337</v>
@@ -10110,7 +10110,7 @@
         <v>-1</v>
       </c>
       <c r="N182" s="2" t="n">
-        <v>-0.0829176610188375</v>
+        <v>-0.08291766090755399</v>
       </c>
       <c r="O182" s="2" t="inlineStr">
         <is>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>36.37404800319894</v>
+        <v>36.3740481127867</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>12.2136294448214</v>
+        <v>12.21362936009799</v>
       </c>
       <c r="J183" s="2" t="n">
         <v>0.6233960391909781</v>
@@ -10163,7 +10163,7 @@
         <v>-1</v>
       </c>
       <c r="N183" s="2" t="n">
-        <v>-0.0089243580170069</v>
+        <v>-0.0089243579880759</v>
       </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
@@ -10184,7 +10184,7 @@
         <v/>
       </c>
       <c r="D184" s="2" t="n">
-        <v>232.7378641290977</v>
+        <v>232.7378641290976</v>
       </c>
       <c r="E184" s="2" t="n">
         <v>8.25</v>
@@ -10198,10 +10198,10 @@
         <v>0</v>
       </c>
       <c r="H184" s="2" t="n">
-        <v>40.5458025291711</v>
+        <v>40.54580255516905</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>13.1372224076969</v>
+        <v>13.13722243130513</v>
       </c>
       <c r="J184" s="2" t="n">
         <v>1.351310000819434</v>
@@ -10216,7 +10216,7 @@
         <v>-1</v>
       </c>
       <c r="N184" s="2" t="n">
-        <v>-0.0174473693750246</v>
+        <v>-0.017447369379476</v>
       </c>
       <c r="O184" s="2" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v/>
       </c>
       <c r="D185" s="2" t="n">
-        <v>230.8509204089655</v>
+        <v>230.8509204089653</v>
       </c>
       <c r="E185" s="2" t="n">
         <v>12.95</v>
@@ -10251,10 +10251,10 @@
         <v>0</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>38.8662825496948</v>
+        <v>38.86628271959582</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>16.7440418231277</v>
+        <v>16.7440418527978</v>
       </c>
       <c r="J185" s="2" t="n">
         <v>0.3366570056873748</v>
@@ -10269,7 +10269,7 @@
         <v>-1</v>
       </c>
       <c r="N185" s="2" t="n">
-        <v>-0.0582728065058194</v>
+        <v>-0.0582728065280729</v>
       </c>
       <c r="O185" s="2" t="inlineStr">
         <is>
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="H186" s="2" t="n">
-        <v>32.50002500241268</v>
+        <v>32.50002505480157</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>19.68204997959716</v>
+        <v>19.68205005963125</v>
       </c>
       <c r="J186" s="2" t="n">
         <v>1.360649646660604</v>
@@ -10322,7 +10322,7 @@
         <v>-1</v>
       </c>
       <c r="N186" s="2" t="n">
-        <v>-0.131003040981584</v>
+        <v>-0.1310030409927106</v>
       </c>
       <c r="O186" s="2" t="inlineStr">
         <is>
@@ -10357,10 +10357,10 @@
         <v>0</v>
       </c>
       <c r="H187" s="2" t="n">
-        <v>35.28830710262932</v>
+        <v>35.2883070518163</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>36.24321377378875</v>
+        <v>36.24321376668698</v>
       </c>
       <c r="J187" s="2" t="n">
         <v>1.05516098499058</v>
@@ -10375,7 +10375,7 @@
         <v>-1</v>
       </c>
       <c r="N187" s="2" t="n">
-        <v>0.008266578260641901</v>
+        <v>0.0082665782828968</v>
       </c>
       <c r="O187" s="2" t="inlineStr">
         <is>
@@ -10410,10 +10410,10 @@
         <v>0</v>
       </c>
       <c r="H188" s="2" t="n">
-        <v>28.66555720108498</v>
+        <v>28.66555793010052</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>11.53641678235147</v>
+        <v>11.53641673490234</v>
       </c>
       <c r="J188" s="2" t="n">
         <v>1.903878369971426</v>
@@ -10428,7 +10428,7 @@
         <v>-1</v>
       </c>
       <c r="N188" s="2" t="n">
-        <v>-0.1108329844758646</v>
+        <v>-0.1108329843868515</v>
       </c>
       <c r="O188" s="2" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v/>
       </c>
       <c r="D189" s="2" t="n">
-        <v>217.783715403493</v>
+        <v>217.7837154034942</v>
       </c>
       <c r="E189" s="2" t="n">
         <v>16.65</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="H189" s="2" t="n">
-        <v>42.53502037774128</v>
+        <v>42.53502025816484</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>13.331559410694</v>
+        <v>13.33155953290461</v>
       </c>
       <c r="J189" s="2" t="n">
         <v>0.5798636891061452</v>
@@ -10481,7 +10481,7 @@
         <v>-1</v>
       </c>
       <c r="N189" s="2" t="n">
-        <v>-0.0222041647345254</v>
+        <v>-0.0222041646788891</v>
       </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>-1</v>
       </c>
       <c r="N190" s="2" t="n">
-        <v>-0.0116600753692221</v>
+        <v>-0.0116600753580954</v>
       </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
@@ -10569,10 +10569,10 @@
         <v>0</v>
       </c>
       <c r="H191" s="2" t="n">
-        <v>29.61064854684143</v>
+        <v>29.6106485253352</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>14.96384714241715</v>
+        <v>14.96384715761888</v>
       </c>
       <c r="J191" s="2" t="n">
         <v>0.964531715016688</v>
@@ -10608,7 +10608,7 @@
         <v/>
       </c>
       <c r="D192" s="2" t="n">
-        <v>213.7334492973822</v>
+        <v>213.7334492973866</v>
       </c>
       <c r="E192" s="2" t="n">
         <v>164</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="H192" s="2" t="n">
-        <v>40.41750672462732</v>
+        <v>40.41750675618885</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>13.03597075085218</v>
+        <v>13.03597076255722</v>
       </c>
       <c r="J192" s="2" t="n">
         <v>0.5939442380616455</v>
@@ -10640,7 +10640,7 @@
         <v>-1</v>
       </c>
       <c r="N192" s="2" t="n">
-        <v>-0.627239572656227</v>
+        <v>-0.6272395732126141</v>
       </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>40.39649190794629</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>21.52079982797342</v>
+        <v>21.52079984219306</v>
       </c>
       <c r="J193" s="2" t="n">
         <v>0.2978796823487169</v>
@@ -10693,7 +10693,7 @@
         <v>-1</v>
       </c>
       <c r="N193" s="2" t="n">
-        <v>0.1132021207600531</v>
+        <v>0.1132021208045586</v>
       </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
@@ -10728,10 +10728,10 @@
         <v>0</v>
       </c>
       <c r="H194" s="2" t="n">
-        <v>48.02799375444827</v>
+        <v>48.02799380209156</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>15.66489096773734</v>
+        <v>15.66489100983429</v>
       </c>
       <c r="J194" s="2" t="n">
         <v>0.5761783767673757</v>
@@ -10746,7 +10746,7 @@
         <v>-1</v>
       </c>
       <c r="N194" s="2" t="n">
-        <v>-0.0539445034062858</v>
+        <v>-0.0539445034730469</v>
       </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v/>
       </c>
       <c r="D195" s="2" t="n">
-        <v>203.095764602792</v>
+        <v>203.0957646027918</v>
       </c>
       <c r="E195" s="2" t="n">
         <v>17</v>
@@ -10781,10 +10781,10 @@
         <v>0</v>
       </c>
       <c r="H195" s="2" t="n">
-        <v>40.58379854772852</v>
+        <v>40.58379855890672</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>14.59995439516311</v>
+        <v>14.59995438884363</v>
       </c>
       <c r="J195" s="2" t="n">
         <v>1.081083004155928</v>
@@ -10799,7 +10799,7 @@
         <v>-1</v>
       </c>
       <c r="N195" s="2" t="n">
-        <v>-0.08058619950261491</v>
+        <v>-0.0805861995248688</v>
       </c>
       <c r="O195" s="2" t="inlineStr">
         <is>
@@ -10834,10 +10834,10 @@
         <v>0</v>
       </c>
       <c r="H196" s="2" t="n">
-        <v>39.26865402351033</v>
+        <v>39.26865404545117</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>18.28109492788303</v>
+        <v>18.28109503499408</v>
       </c>
       <c r="J196" s="2" t="n">
         <v>0.5246800456781106</v>
@@ -10852,7 +10852,7 @@
         <v>-1</v>
       </c>
       <c r="N196" s="2" t="n">
-        <v>-0.1078084481957678</v>
+        <v>-0.1078084482847819</v>
       </c>
       <c r="O196" s="2" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v/>
       </c>
       <c r="D197" s="2" t="n">
-        <v>202.2235780303681</v>
+        <v>202.2235780303682</v>
       </c>
       <c r="E197" s="2" t="n">
         <v>32.65</v>
@@ -10887,10 +10887,10 @@
         <v>0</v>
       </c>
       <c r="H197" s="2" t="n">
-        <v>49.39760178158516</v>
+        <v>49.39760177979539</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>5.111754553605644</v>
+        <v>5.111754654206917</v>
       </c>
       <c r="J197" s="2" t="n">
         <v>0.5349881098118677</v>
@@ -10905,7 +10905,7 @@
         <v>-1</v>
       </c>
       <c r="N197" s="2" t="n">
-        <v>0.1223586404343743</v>
+        <v>0.1223586402785915</v>
       </c>
       <c r="O197" s="2" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
         <v>48.62437436347871</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>16.59348671379819</v>
+        <v>16.59348666545671</v>
       </c>
       <c r="J198" s="2" t="n">
         <v>0.9178751424102574</v>
@@ -10979,7 +10979,7 @@
         <v/>
       </c>
       <c r="D199" s="2" t="n">
-        <v>194.5279409627782</v>
+        <v>194.527940962778</v>
       </c>
       <c r="E199" s="2" t="n">
         <v>25.7</v>
@@ -10993,10 +10993,10 @@
         <v>0</v>
       </c>
       <c r="H199" s="2" t="n">
-        <v>45.27304635107748</v>
+        <v>45.27304668683079</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>15.04922601548201</v>
+        <v>15.04922595927195</v>
       </c>
       <c r="J199" s="2" t="n">
         <v>0.9828286531243546</v>
@@ -11011,7 +11011,7 @@
         <v>-1</v>
       </c>
       <c r="N199" s="2" t="n">
-        <v>0.0066598906785901</v>
+        <v>0.0066598906229544</v>
       </c>
       <c r="O199" s="2" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v/>
       </c>
       <c r="D200" s="2" t="n">
-        <v>190.6053747804585</v>
+        <v>190.6053747804586</v>
       </c>
       <c r="E200" s="2" t="n">
         <v>33.45</v>
@@ -11046,10 +11046,10 @@
         <v>0</v>
       </c>
       <c r="H200" s="2" t="n">
-        <v>36.39471010710784</v>
+        <v>36.39470979245396</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>21.14527514382402</v>
+        <v>21.145275364126</v>
       </c>
       <c r="J200" s="2" t="n">
         <v>0.4543505400507371</v>
@@ -11064,7 +11064,7 @@
         <v>-1</v>
       </c>
       <c r="N200" s="2" t="n">
-        <v>0.0399793147538807</v>
+        <v>0.039979315020926</v>
       </c>
       <c r="O200" s="2" t="inlineStr">
         <is>
@@ -11099,10 +11099,10 @@
         <v>0</v>
       </c>
       <c r="H201" s="2" t="n">
-        <v>43.00242110293937</v>
+        <v>43.00242121708657</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>14.17751109524386</v>
+        <v>14.17751119253689</v>
       </c>
       <c r="J201" s="2" t="n">
         <v>0.1669001853132166</v>
@@ -11117,7 +11117,7 @@
         <v>-1</v>
       </c>
       <c r="N201" s="2" t="n">
-        <v>-0.08228500474937479</v>
+        <v>-0.08228500478750771</v>
       </c>
       <c r="O201" s="2" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>0</v>
       </c>
       <c r="H202" s="2" t="n">
-        <v>42.60846389181653</v>
+        <v>42.60846390890936</v>
       </c>
       <c r="I202" s="2" t="n">
         <v>17.56838479655606</v>
@@ -11205,10 +11205,10 @@
         <v>0</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>46.05505365487854</v>
+        <v>46.05505358428115</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>11.12271325863464</v>
+        <v>11.12271311712576</v>
       </c>
       <c r="J203" s="2" t="n">
         <v>0.2481570114490726</v>
@@ -11223,7 +11223,7 @@
         <v>-1</v>
       </c>
       <c r="N203" s="2" t="n">
-        <v>-0.0493567560778737</v>
+        <v>-0.049356755999983</v>
       </c>
       <c r="O203" s="2" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
         <v/>
       </c>
       <c r="D204" s="2" t="n">
-        <v>177.771581294619</v>
+        <v>177.7715812946192</v>
       </c>
       <c r="E204" s="2" t="n">
         <v>18.8</v>
@@ -11258,10 +11258,10 @@
         <v>0</v>
       </c>
       <c r="H204" s="2" t="n">
-        <v>42.84218330606452</v>
+        <v>42.84218328677609</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>18.63661439318779</v>
+        <v>18.63661432342376</v>
       </c>
       <c r="J204" s="2" t="n">
         <v>0.2455985109624509</v>
@@ -11276,7 +11276,7 @@
         <v>-1</v>
       </c>
       <c r="N204" s="2" t="n">
-        <v>-0.0334495008138518</v>
+        <v>-0.0334495008472334</v>
       </c>
       <c r="O204" s="2" t="inlineStr">
         <is>
@@ -11311,10 +11311,10 @@
         <v>0</v>
       </c>
       <c r="H205" s="2" t="n">
-        <v>31.17710320448034</v>
+        <v>31.1771029423336</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>21.12058205650126</v>
+        <v>21.12058265361562</v>
       </c>
       <c r="J205" s="2" t="n">
         <v>0.8107972203318302</v>
@@ -11329,7 +11329,7 @@
         <v>-1</v>
       </c>
       <c r="N205" s="2" t="n">
-        <v>-0.0873546111228399</v>
+        <v>-0.0873546109225545</v>
       </c>
       <c r="O205" s="2" t="inlineStr">
         <is>
@@ -11364,10 +11364,10 @@
         <v>0</v>
       </c>
       <c r="H206" s="2" t="n">
-        <v>36.66955781998517</v>
+        <v>36.66955776513534</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>11.30908521914432</v>
+        <v>11.3090852930451</v>
       </c>
       <c r="J206" s="2" t="n">
         <v>1.267335641597861</v>
@@ -11417,10 +11417,10 @@
         <v>0</v>
       </c>
       <c r="H207" s="2" t="n">
-        <v>40.58186186923659</v>
+        <v>40.58186194552273</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>31.42273762136913</v>
+        <v>31.42273758426411</v>
       </c>
       <c r="J207" s="2" t="n">
         <v>0.3709338768050627</v>
@@ -11435,7 +11435,7 @@
         <v>-1</v>
       </c>
       <c r="N207" s="2" t="n">
-        <v>-0.0080136446225158</v>
+        <v>-0.0080136446447706</v>
       </c>
       <c r="O207" s="2" t="inlineStr">
         <is>
@@ -11470,10 +11470,10 @@
         <v>0</v>
       </c>
       <c r="H208" s="2" t="n">
-        <v>50.19470845388718</v>
+        <v>50.19470845752349</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>7.022069093251774</v>
+        <v>7.022069110464598</v>
       </c>
       <c r="J208" s="2" t="n">
         <v>0.1380663807213029</v>
@@ -11488,7 +11488,7 @@
         <v>-1</v>
       </c>
       <c r="N208" s="2" t="n">
-        <v>0.0697046195876953</v>
+        <v>0.0697046196767148</v>
       </c>
       <c r="O208" s="2" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         <v/>
       </c>
       <c r="D209" s="2" t="n">
-        <v>156.9592259640493</v>
+        <v>156.9592259640494</v>
       </c>
       <c r="E209" s="2" t="n">
         <v>10.95</v>
@@ -11523,10 +11523,10 @@
         <v>0</v>
       </c>
       <c r="H209" s="2" t="n">
-        <v>38.75471598422828</v>
+        <v>38.75471600911353</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>15.15165065486064</v>
+        <v>15.15165067004632</v>
       </c>
       <c r="J209" s="2" t="n">
         <v>0.3841001426028629</v>
@@ -11541,7 +11541,7 @@
         <v>-1</v>
       </c>
       <c r="N209" s="2" t="n">
-        <v>-0.0444720529270108</v>
+        <v>-0.044472052938138</v>
       </c>
       <c r="O209" s="2" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v/>
       </c>
       <c r="D210" s="2" t="n">
-        <v>154.0334259284857</v>
+        <v>154.033425928486</v>
       </c>
       <c r="E210" s="2" t="n">
         <v>21.75</v>
@@ -11576,10 +11576,10 @@
         <v>0</v>
       </c>
       <c r="H210" s="2" t="n">
-        <v>43.17984735591688</v>
+        <v>43.1798472400305</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>18.63134023238382</v>
+        <v>18.63134023852804</v>
       </c>
       <c r="J210" s="2" t="n">
         <v>0.7838025558560217</v>
@@ -11594,7 +11594,7 @@
         <v>-1</v>
       </c>
       <c r="N210" s="2" t="n">
-        <v>0.0436801917212925</v>
+        <v>0.0436801918436904</v>
       </c>
       <c r="O210" s="2" t="inlineStr">
         <is>
@@ -11629,10 +11629,10 @@
         <v>0</v>
       </c>
       <c r="H211" s="2" t="n">
-        <v>51.09486708509536</v>
+        <v>51.09486708282223</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>4.802568958032949</v>
+        <v>4.802568958032945</v>
       </c>
       <c r="J211" s="2" t="n">
         <v>1.387273828792578</v>
@@ -11647,7 +11647,7 @@
         <v>-1</v>
       </c>
       <c r="N211" s="2" t="n">
-        <v>-0.0091460384814215</v>
+        <v>-0.009146038436912999</v>
       </c>
       <c r="O211" s="2" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         <v/>
       </c>
       <c r="D212" s="2" t="n">
-        <v>149.4785807513406</v>
+        <v>149.4785807513407</v>
       </c>
       <c r="E212" s="2" t="n">
         <v>65</v>
@@ -11685,7 +11685,7 @@
         <v>40.41334366353672</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>15.5939822037589</v>
+        <v>15.59398222647041</v>
       </c>
       <c r="J212" s="2" t="n">
         <v>0.6672651983990608</v>
@@ -11700,7 +11700,7 @@
         <v>-1</v>
       </c>
       <c r="N212" s="2" t="n">
-        <v>-0.0206512437530864</v>
+        <v>-0.0206512438421095</v>
       </c>
       <c r="O212" s="2" t="inlineStr">
         <is>
@@ -11735,10 +11735,10 @@
         <v>0</v>
       </c>
       <c r="H213" s="2" t="n">
-        <v>41.98380756143506</v>
+        <v>41.9838073805468</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>13.68865918080032</v>
+        <v>13.68865923013519</v>
       </c>
       <c r="J213" s="2" t="n">
         <v>0.6917690167449165</v>
@@ -11753,7 +11753,7 @@
         <v>-1</v>
       </c>
       <c r="N213" s="2" t="n">
-        <v>-0.0030526252859083</v>
+        <v>-0.0030526252525276</v>
       </c>
       <c r="O213" s="2" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>44.65511657980243</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>14.22684812083428</v>
+        <v>14.22684826127909</v>
       </c>
       <c r="J214" s="2" t="n">
         <v>0.7707217702925507</v>
@@ -11827,7 +11827,7 @@
         <v/>
       </c>
       <c r="D215" s="2" t="n">
-        <v>141.8455213798516</v>
+        <v>141.8455213798514</v>
       </c>
       <c r="E215" s="2" t="n">
         <v>33.65</v>
@@ -11841,10 +11841,10 @@
         <v>0</v>
       </c>
       <c r="H215" s="2" t="n">
-        <v>43.07107218177205</v>
+        <v>43.07107228611675</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>9.703643301706521</v>
+        <v>9.703643375410746</v>
       </c>
       <c r="J215" s="2" t="n">
         <v>0.3215971391065982</v>
@@ -11859,7 +11859,7 @@
         <v>-1</v>
       </c>
       <c r="N215" s="2" t="n">
-        <v>-0.1238853658225705</v>
+        <v>-0.1238853658336985</v>
       </c>
       <c r="O215" s="2" t="inlineStr">
         <is>
@@ -11894,10 +11894,10 @@
         <v>0</v>
       </c>
       <c r="H216" s="2" t="n">
-        <v>43.04115086343767</v>
+        <v>43.04115082833285</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>16.62649946088544</v>
+        <v>16.62649954606928</v>
       </c>
       <c r="J216" s="2" t="n">
         <v>0.2657428434190147</v>
@@ -11912,7 +11912,7 @@
         <v>-1</v>
       </c>
       <c r="N216" s="2" t="n">
-        <v>0.0149741189713692</v>
+        <v>0.0149741190047486</v>
       </c>
       <c r="O216" s="2" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v/>
       </c>
       <c r="D217" s="2" t="n">
-        <v>125.6581339182065</v>
+        <v>125.658133918206</v>
       </c>
       <c r="E217" s="2" t="n">
         <v>45.2</v>
@@ -11947,10 +11947,10 @@
         <v>0</v>
       </c>
       <c r="H217" s="2" t="n">
-        <v>33.49943313992124</v>
+        <v>33.49943309659074</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>10.74378697229678</v>
+        <v>10.74378699687276</v>
       </c>
       <c r="J217" s="2" t="n">
         <v>0.7121161540160343</v>
@@ -11965,7 +11965,7 @@
         <v>-1</v>
       </c>
       <c r="N217" s="2" t="n">
-        <v>-0.0628103619214935</v>
+        <v>-0.0628103614096428</v>
       </c>
       <c r="O217" s="2" t="inlineStr">
         <is>
@@ -12000,10 +12000,10 @@
         <v>0</v>
       </c>
       <c r="H218" s="2" t="n">
-        <v>51.43830962771152</v>
+        <v>51.43830964689423</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>13.40893994185128</v>
+        <v>13.40893994886778</v>
       </c>
       <c r="J218" s="2" t="n">
         <v>1.097071629435313</v>
@@ -12018,7 +12018,7 @@
         <v>-1</v>
       </c>
       <c r="N218" s="2" t="n">
-        <v>-0.0077973753253276</v>
+        <v>-0.0077973753364535</v>
       </c>
       <c r="O218" s="2" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>0</v>
       </c>
       <c r="H219" s="2" t="n">
-        <v>46.26273821512766</v>
+        <v>46.26273824683504</v>
       </c>
       <c r="I219" s="2" t="n">
         <v>13.1991985832413</v>
@@ -12071,7 +12071,7 @@
         <v>-1</v>
       </c>
       <c r="N219" s="2" t="n">
-        <v>-0.021932401823545</v>
+        <v>-0.0219324018457982</v>
       </c>
       <c r="O219" s="2" t="inlineStr">
         <is>
@@ -12106,10 +12106,10 @@
         <v>0</v>
       </c>
       <c r="H220" s="2" t="n">
-        <v>39.8564730508721</v>
+        <v>39.85647314173026</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>16.48862623066752</v>
+        <v>16.4886263725902</v>
       </c>
       <c r="J220" s="2" t="n">
         <v>0.8724520171968554</v>
@@ -12124,7 +12124,7 @@
         <v>-1</v>
       </c>
       <c r="N220" s="2" t="n">
-        <v>-0.0566975393274944</v>
+        <v>-0.0566975392496068</v>
       </c>
       <c r="O220" s="2" t="inlineStr">
         <is>

--- a/output/full_scan/batch_seq3_2026-10-08.xlsx
+++ b/output/full_scan/batch_seq3_2026-10-08.xlsx
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>76.45534892006495</v>
+        <v>76.45534892490231</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>29.1621416387618</v>
+        <v>29.16214130330404</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1.53634927716005</v>
@@ -570,7 +570,7 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.1271192942622303</v>
+        <v>0.1271192942812965</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>61.45756353027819</v>
+        <v>61.45756351868081</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>11.17216333149276</v>
+        <v>11.17216341208694</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>1.647711687838602</v>
@@ -623,7 +623,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1141888968712947</v>
+        <v>0.1141888967751563</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>63.11306699265009</v>
+        <v>63.11306710375683</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>16.19297184277554</v>
+        <v>16.19297173320319</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>5.058008947146207</v>
@@ -676,7 +676,7 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.0178334152524633</v>
+        <v>0.0178334152284272</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>63.0870213297239</v>
+        <v>63.08702132911546</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>30.33196654985727</v>
+        <v>30.33196656279758</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>1.419707879810233</v>
@@ -729,7 +729,7 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>3.387390396935899</v>
+        <v>3.387390397032114</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>70.81944679625229</v>
+        <v>70.81944681719693</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>26.42949806210782</v>
+        <v>26.42949808869654</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>2.967716570204979</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1.561420738331697</v>
+        <v>1.561420738932563</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>69.35993884233798</v>
+        <v>69.35993883257972</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>26.3644419648098</v>
+        <v>26.36444206888599</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>2.402820677695992</v>
@@ -835,7 +835,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1.799429338684028</v>
+        <v>1.79942933885227</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>67.70096581390698</v>
+        <v>67.70096577391564</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>18.77185563663852</v>
+        <v>18.77185561111252</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>6.478128287332894</v>
@@ -888,7 +888,7 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.6833642595193602</v>
+        <v>0.6833642595313755</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>68.87562334555099</v>
+        <v>68.87562336037008</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>41.07101413442446</v>
+        <v>41.07101413153666</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>0.6847643170286102</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.0519830160203174</v>
+        <v>0.0519830159722491</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>63.9435201830793</v>
+        <v>63.94352015561864</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>19.62842380362466</v>
+        <v>19.62842383038114</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>2.108941271811392</v>
@@ -1015,7 +1015,7 @@
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>922.8264666569788</v>
+        <v>922.8264666569791</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1270</v>
@@ -1029,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>66.7948525059887</v>
+        <v>66.79485249017961</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>28.31248980419486</v>
+        <v>28.31248979630273</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>0.5863127058136999</v>
@@ -1047,7 +1047,7 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>21.01379009532783</v>
+        <v>21.0137900968902</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>71.72778285067352</v>
+        <v>71.72778263369318</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>20.59401848212228</v>
+        <v>20.59401852697989</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>1.576950395112557</v>
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>5.947212059183052</v>
+        <v>5.94721206302857</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>912.2314181134284</v>
+        <v>912.231418113428</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>132.5</v>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>68.28194806733917</v>
+        <v>68.28194796024404</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>16.50688575603381</v>
+        <v>16.50688571050071</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>1.092602826241415</v>
@@ -1153,7 +1153,7 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.8181839480068545</v>
+        <v>0.8181839481991342</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>911.7642013323648</v>
+        <v>911.764201332365</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>145</v>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>61.35605797573869</v>
+        <v>61.35605806547021</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>41.23786997544398</v>
+        <v>41.23787005944318</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>1.105450608621021</v>
@@ -1206,7 +1206,7 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.8084442013343449</v>
+        <v>0.8084442006132875</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>61.52550002961303</v>
+        <v>61.52549996594143</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>24.13261711204913</v>
+        <v>24.13261714079281</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>1.92698167297162</v>
@@ -1259,7 +1259,7 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.1597830861197948</v>
+        <v>0.1597830867206653</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>61.42922034142718</v>
+        <v>61.42922036333852</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>34.56571950862092</v>
+        <v>34.56571964124586</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>0.6944967244618357</v>
@@ -1312,7 +1312,7 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.2346081753325852</v>
+        <v>-0.234608175416711</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>73.27553041667846</v>
+        <v>73.27553028877541</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>34.44475898117826</v>
+        <v>34.44475902395462</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>0.6825701563009359</v>
@@ -1365,7 +1365,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>4.437624590189852</v>
+        <v>4.437624592593352</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>60.35458671640266</v>
+        <v>60.3545867366065</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>14.99952694978566</v>
+        <v>14.9995270640563</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>0.6176122664364789</v>
@@ -1418,7 +1418,7 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.4991911521051879</v>
+        <v>0.4991911517446648</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>872.0574540776836</v>
+        <v>872.0574540776837</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>36.7</v>
@@ -1453,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>55.31952639820381</v>
+        <v>55.31952638362174</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>25.19117940918392</v>
+        <v>25.19117943976267</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>0.5188841340719633</v>
@@ -1471,7 +1471,7 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.0694868455058836</v>
+        <v>-0.0694868454818519</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>855.0656982986844</v>
+        <v>855.0656982986842</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>31.95</v>
@@ -1506,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>61.12753459245248</v>
+        <v>61.12753460559903</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>13.42756609179199</v>
+        <v>13.42756590444716</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>2.102745068766554</v>
@@ -1524,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.1031327678790205</v>
+        <v>0.1031327678189358</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>72.88192271007424</v>
+        <v>72.88192270397283</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>27.01562461800257</v>
+        <v>27.01562460013453</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>1.760175335808465</v>
@@ -1577,7 +1577,7 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>12.61059032396836</v>
+        <v>12.61059032416063</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>849.8905604598656</v>
+        <v>849.8905604598674</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>243.5</v>
@@ -1612,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>63.37291582079134</v>
+        <v>63.37291582534763</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>18.27122190716159</v>
+        <v>18.27122199608606</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>2.146463650550482</v>
@@ -1630,7 +1630,7 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>4.470356715475746</v>
+        <v>4.470356715235423</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1665,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>59.00102340123653</v>
+        <v>59.00102344717286</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>31.95087708911255</v>
+        <v>31.95087707700852</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>0.532582109580958</v>
@@ -1683,7 +1683,7 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.5257799248245436</v>
+        <v>0.5257799245841981</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>847.6188568417917</v>
+        <v>847.6188568417916</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>51.1</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>66.02313587369517</v>
+        <v>66.02313583401641</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>32.47064672169719</v>
+        <v>32.47064650029119</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>0.8333525372244619</v>
@@ -1736,7 +1736,7 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.4001299487765979</v>
+        <v>0.4001299489208034</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>821.2668249223943</v>
+        <v>821.2668249223938</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>134.5</v>
@@ -1771,10 +1771,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>63.27757663603444</v>
+        <v>63.27757658974946</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>13.37101840094512</v>
+        <v>13.37101842998432</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>2.045917044638552</v>
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>2.064003469954109</v>
+        <v>2.064003470314629</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>795.8332716711186</v>
+        <v>795.8332716711187</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>33.2</v>
@@ -1824,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>72.2244341571747</v>
+        <v>72.2244340872551</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>41.98048401241482</v>
+        <v>41.98048391273301</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>1.111026684245253</v>
@@ -1842,7 +1842,7 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.4983237033794963</v>
+        <v>0.498323703511683</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>784.6374117157633</v>
+        <v>784.6374117157632</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>211</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>58.33273941804636</v>
+        <v>58.33273940286842</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>25.87109614515093</v>
+        <v>25.87109618766745</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>0.6246121104413546</v>
@@ -1895,7 +1895,7 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>1.449324199002813</v>
+        <v>1.449324199122994</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>56.49551513523384</v>
+        <v>56.49551522042334</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>25.83096659228407</v>
+        <v>25.830966713117</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>1.527461685522735</v>
@@ -1948,7 +1948,7 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.0615283690721443</v>
+        <v>-0.0615283692163549</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1983,10 +1983,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>64.03400990407863</v>
+        <v>64.03400992369541</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>46.01775434778837</v>
+        <v>46.01775447915185</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>0.6720627160835494</v>
@@ -2001,7 +2001,7 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.127362190976549</v>
+        <v>-0.1273621910246186</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>67.21106886393511</v>
+        <v>67.21106882701599</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>33.66669991460707</v>
+        <v>33.66669974511292</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>0.5839557732674189</v>
@@ -2054,7 +2054,7 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>6.898875169463025</v>
+        <v>6.898875171578098</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2089,10 +2089,10 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>56.38366707822837</v>
+        <v>56.38366707056251</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>16.36821905525412</v>
+        <v>16.36821906760196</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>0.914308699200523</v>
@@ -2107,7 +2107,7 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>12.03322889957926</v>
+        <v>12.03322890198322</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2142,10 +2142,10 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>50.78621354144086</v>
+        <v>50.78621353347953</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>24.57482450022761</v>
+        <v>24.57482463023499</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>0.2528069540021731</v>
@@ -2160,7 +2160,7 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.1482020978934249</v>
+        <v>-0.1482020978333366</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>57.30004811205699</v>
+        <v>57.30004795276846</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>23.44193486415746</v>
+        <v>23.44193490185537</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>0.7122291921512059</v>
@@ -2213,7 +2213,7 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.047442445329675</v>
+        <v>0.0474424456901807</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2248,10 +2248,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>64.88934775944949</v>
+        <v>64.88934773640371</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>52.52018634436224</v>
+        <v>52.52018636397835</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>0.6153529734989762</v>
@@ -2266,7 +2266,7 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.1231690370839106</v>
+        <v>0.123169037095927</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2301,10 +2301,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>51.96578841618619</v>
+        <v>51.9657883727794</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>31.07698103340855</v>
+        <v>31.07698092149244</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>0.5626819817271111</v>
@@ -2319,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.6278223203618376</v>
+        <v>-0.6278223200734234</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>60.25683567276156</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>30.25480365996508</v>
+        <v>30.25480368813497</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>0.8171492139635138</v>
@@ -2372,7 +2372,7 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.2820180516156223</v>
+        <v>-0.2820180517357942</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2407,10 +2407,10 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>64.57407792825794</v>
+        <v>64.57407780753059</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>33.78006372074815</v>
+        <v>33.78006377324745</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>0.8194751485443865</v>
@@ -2425,7 +2425,7 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.2234346222091539</v>
+        <v>-0.2234346218486311</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>751.6818192002207</v>
+        <v>751.6818192002206</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>16.3</v>
@@ -2460,10 +2460,10 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>53.92214607657421</v>
+        <v>53.92214608264041</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>6.216463590128181</v>
+        <v>6.216463590128179</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>4.743981953586107</v>
@@ -2478,7 +2478,7 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.2416517147422827</v>
+        <v>0.2416517145860575</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>748.9955927303752</v>
+        <v>748.9955927303751</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>329</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>58.07186457018228</v>
+        <v>58.07186447395152</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>14.95834055680261</v>
+        <v>14.95834068194992</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>0.9078362733231808</v>
@@ -2531,7 +2531,7 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.94423521507265</v>
+        <v>0.9442352160340628</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2566,10 +2566,10 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>57.09918306339342</v>
+        <v>57.09918307203961</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>35.76718944311072</v>
+        <v>35.76718941793749</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>0.7508867942452564</v>
@@ -2584,7 +2584,7 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-4.216053622345299</v>
+        <v>-4.216053622825925</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>59.68173788405321</v>
+        <v>59.6817379703766</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>39.04824402926882</v>
+        <v>39.04824448761882</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>3.448151378147453</v>
@@ -2637,7 +2637,7 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.0340294750886562</v>
+        <v>-0.0340294752202701</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>719.0372240421656</v>
+        <v>719.0372240421583</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>39.6</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>58.96383424413432</v>
+        <v>58.96383380302225</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>22.46434156372451</v>
+        <v>22.4643415590968</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>1.287948019005943</v>
@@ -2690,7 +2690,7 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.1147454298591009</v>
+        <v>0.1147454303157605</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2725,10 +2725,10 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>60.88509776140627</v>
+        <v>60.88509776380494</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>25.48232430374589</v>
+        <v>25.4823243029799</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>0.7966177658776836</v>
@@ -2743,7 +2743,7 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.9107502304550376</v>
+        <v>0.9107502304910904</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>56.21725882529236</v>
+        <v>56.21725883419096</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>30.03465451256099</v>
+        <v>30.03465458286208</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>0.6925067586592338</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.6690205454703566</v>
+        <v>0.6690205452300049</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>66.47723744081132</v>
+        <v>66.47723734204013</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>21.61304023503783</v>
+        <v>21.61304027654448</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>0.7524466240010222</v>
@@ -2849,7 +2849,7 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>1.614050516253346</v>
+        <v>1.614050516613889</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>55.60695905468042</v>
+        <v>55.60695897485667</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>33.84212775844003</v>
+        <v>33.84212764402228</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>0.4559214057120711</v>
@@ -2902,7 +2902,7 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.0952465899578385</v>
+        <v>-0.095246588683997</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2937,10 +2937,10 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>59.25842368620811</v>
+        <v>59.25842360596008</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>38.79650101072402</v>
+        <v>38.79650101072401</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>0.6893646682283873</v>
@@ -2955,7 +2955,7 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.1826639002021812</v>
+        <v>-0.1826639001300787</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>670.9560220440825</v>
+        <v>670.9560220440819</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>130.5</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>63.98540187076158</v>
+        <v>63.98540159332364</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>16.98741149964235</v>
+        <v>16.98741157867598</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>2.276313149637385</v>
@@ -3008,7 +3008,7 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>1.04396375676865</v>
+        <v>1.043963757850214</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3043,10 +3043,10 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>63.14437905363093</v>
+        <v>63.14437894890825</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>15.55322343603116</v>
+        <v>15.55322342594143</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>0.9823894969014648</v>
@@ -3061,7 +3061,7 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>3.487355115653499</v>
+        <v>3.487355117456074</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3096,10 +3096,10 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>54.23827392978807</v>
+        <v>54.23827377104715</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>8.781239478105814</v>
+        <v>8.781239494877381</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>0.6675488898691369</v>
@@ -3114,7 +3114,7 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>2.629762658511098</v>
+        <v>2.629762658078477</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>50.70458207331546</v>
+        <v>50.70458195986977</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>28.42789273968878</v>
+        <v>28.42789268702545</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>0.4376343808176557</v>
@@ -3167,7 +3167,7 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.4596418389092556</v>
+        <v>-0.4596418383083883</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3202,10 +3202,10 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>51.50443659673014</v>
+        <v>51.50443665804583</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>10.4749647384877</v>
+        <v>10.47496487339931</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>0.7675686211542143</v>
@@ -3220,7 +3220,7 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.3552548971436553</v>
+        <v>0.355254897059542</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>639.1678096745985</v>
+        <v>639.1678096745984</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>44.05</v>
@@ -3255,10 +3255,10 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>52.76036906127862</v>
+        <v>52.76036907275115</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>33.37423521151685</v>
+        <v>33.37423539199658</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>0.8439268367929332</v>
@@ -3273,7 +3273,7 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.2305657975305357</v>
+        <v>-0.230565797566584</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>638.4999580082607</v>
+        <v>638.4999580082606</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>16.5</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>52.66368241848235</v>
+        <v>52.66368236080022</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>22.30760423913329</v>
+        <v>22.30760432065279</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>0.4987601837788259</v>
@@ -3326,7 +3326,7 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.0866190578116634</v>
+        <v>-0.0866190578597346</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3361,10 +3361,10 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>65.7181403162937</v>
+        <v>65.71814034768181</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>36.52184586778987</v>
+        <v>36.52184591209392</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>0.8636811282878285</v>
@@ -3379,7 +3379,7 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.1419440125341176</v>
+        <v>0.1419440125461336</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3414,10 +3414,10 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>62.18279280892308</v>
+        <v>62.1827927787317</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>21.04682989897179</v>
+        <v>21.04682990067935</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>0.6251130047632402</v>
@@ -3432,7 +3432,7 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.1283581594457782</v>
+        <v>0.1283581594577966</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>52.49015288331909</v>
+        <v>52.49015285186583</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>42.59393308142994</v>
+        <v>42.59393313222828</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>0.531455843295538</v>
@@ -3485,7 +3485,7 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.2045367276089487</v>
+        <v>-0.2045367277291192</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3520,10 +3520,10 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>54.02700756127351</v>
+        <v>54.02700753732417</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>17.65162022409574</v>
+        <v>17.65162013869534</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>0.889601139185641</v>
@@ -3538,7 +3538,7 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>19.13578222489537</v>
+        <v>19.1357822357109</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3573,10 +3573,10 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>53.14291228986846</v>
+        <v>53.14291243526379</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>28.62678462001572</v>
+        <v>28.6267846405331</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>0.4611427244367433</v>
@@ -3591,7 +3591,7 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.2683288473724715</v>
+        <v>-0.2683288477329858</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>48.2211878070498</v>
+        <v>48.22118770025339</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>24.3720858523328</v>
+        <v>24.37208586380019</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>1.067285085815881</v>
@@ -3644,7 +3644,7 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.191925904828486</v>
+        <v>-0.191925904720334</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>56.14069446478128</v>
+        <v>56.14069445230016</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>13.04859927420394</v>
+        <v>13.0485991890795</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>1.061168667670709</v>
@@ -3697,7 +3697,7 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>1.651382714837662</v>
+        <v>1.651382714861684</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>602.2376785886128</v>
+        <v>602.2376785886125</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>153</v>
@@ -3732,10 +3732,10 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>58.82554064883829</v>
+        <v>58.82554060729015</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>28.77032973246373</v>
+        <v>28.77032973559348</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>0.967609636205357</v>
@@ -3750,7 +3750,7 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.5162103879179201</v>
+        <v>-0.5162103878698594</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>598.2574879512081</v>
+        <v>598.2574879512077</v>
       </c>
       <c r="E63" s="2" t="n">
         <v>110</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>50.18686832784376</v>
+        <v>50.18686833246943</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>29.28233426508717</v>
+        <v>29.28233424356307</v>
       </c>
       <c r="J63" s="2" t="n">
         <v>1.023974108576607</v>
@@ -3803,7 +3803,7 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.4566453183797132</v>
+        <v>-0.456645318451814</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3838,10 +3838,10 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>56.07975472647512</v>
+        <v>56.07975467128222</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>41.913030130303</v>
+        <v>41.91303019871006</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>0.4363882427902917</v>
@@ -3856,7 +3856,7 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.3606801603416452</v>
+        <v>-0.3606801602575258</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>56.25511834169224</v>
+        <v>56.25511839571813</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>13.86048725861465</v>
+        <v>13.86048736556059</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>0.9037483184595756</v>
@@ -3909,7 +3909,7 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.1260534630893974</v>
+        <v>-0.126053463209576</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>69.31235169656915</v>
+        <v>69.31235164253239</v>
       </c>
       <c r="I66" s="2" t="n">
         <v>32.67098321330322</v>
@@ -3962,7 +3962,7 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.3979209898584258</v>
+        <v>0.3979209900266685</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -3997,10 +3997,10 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>55.55560286677306</v>
+        <v>55.55560282729372</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>32.52683954094918</v>
+        <v>32.52683956997822</v>
       </c>
       <c r="J67" s="2" t="n">
         <v>0.6854242224348428</v>
@@ -4015,7 +4015,7 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.2044810985012163</v>
+        <v>-0.2044810984050775</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4050,10 +4050,10 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>46.82487025531729</v>
+        <v>46.82487030347334</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>28.58866373026174</v>
+        <v>28.58866370600312</v>
       </c>
       <c r="J68" s="2" t="n">
         <v>0.1954662964182002</v>
@@ -4068,7 +4068,7 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.8369335145447707</v>
+        <v>-0.8369335150254575</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>568.2209997531598</v>
+        <v>568.2209997531604</v>
       </c>
       <c r="E69" s="2" t="n">
         <v>46.55</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>48.69071672000568</v>
+        <v>48.69071631371542</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>28.33669885331103</v>
+        <v>28.33669905604292</v>
       </c>
       <c r="J69" s="2" t="n">
         <v>0.6492018873071583</v>
@@ -4121,7 +4121,7 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.4266774039422216</v>
+        <v>0.4266774042546712</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
@@ -4156,10 +4156,10 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>57.65298554471153</v>
+        <v>57.65298558721523</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>47.56093780887974</v>
+        <v>47.56093782250091</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>0.6315761955833161</v>
@@ -4174,7 +4174,7 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.009861305701631601</v>
+        <v>-0.009861305725666</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4209,10 +4209,10 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>45.1649635475215</v>
+        <v>45.16496362310568</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>18.67712484965302</v>
+        <v>18.67712500953712</v>
       </c>
       <c r="J71" s="2" t="n">
         <v>0.7580300074202138</v>
@@ -4227,7 +4227,7 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-2.636711940079839</v>
+        <v>-2.636711941401757</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>58.01215314964218</v>
+        <v>58.0121532628681</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>16.68274979982523</v>
+        <v>16.68274975785162</v>
       </c>
       <c r="J72" s="2" t="n">
         <v>1.350879938526235</v>
@@ -4280,7 +4280,7 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.0205504884193373</v>
+        <v>0.0205504886837173</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>49.47909182421807</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>23.61550933230466</v>
+        <v>23.61550934988762</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>0.1649987747043492</v>
@@ -4333,7 +4333,7 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.1550921960965358</v>
+        <v>-0.1550921960484686</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>551.9292892887221</v>
+        <v>551.929289288722</v>
       </c>
       <c r="E74" s="2" t="n">
         <v>213</v>
@@ -4368,10 +4368,10 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>43.39584993742227</v>
+        <v>43.39584987806352</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>26.85183594063328</v>
+        <v>26.85183586458247</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>1.171202038746936</v>
@@ -4386,7 +4386,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.1915649326844182</v>
+        <v>0.1915649329247801</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>54.04827648349145</v>
+        <v>54.04827644370185</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>22.57927269773167</v>
+        <v>22.57927262137747</v>
       </c>
       <c r="J75" s="2" t="n">
         <v>0.6736633893150124</v>
@@ -4439,7 +4439,7 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.2471984299446809</v>
+        <v>-0.2471984299927452</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4474,10 +4474,10 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>48.90451808955988</v>
+        <v>48.90451813710756</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>32.61397809504865</v>
+        <v>32.61397809257271</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>0.2268951679351208</v>
@@ -4492,7 +4492,7 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.6584512700812311</v>
+        <v>-0.6584512699129932</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>534.6292994159749</v>
+        <v>534.629299415975</v>
       </c>
       <c r="E77" s="2" t="n">
         <v>552</v>
@@ -4527,10 +4527,10 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>49.43286512910748</v>
+        <v>49.43286509741833</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>12.53280242240897</v>
+        <v>12.53280242265036</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>1.014056338082817</v>
@@ -4545,7 +4545,7 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>3.654110180992446</v>
+        <v>3.654110181593284</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>59.98350034915309</v>
+        <v>59.983500366034</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>16.95207107285232</v>
+        <v>16.95207121885289</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>1.156518303598061</v>
@@ -4598,7 +4598,7 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.6060473080262613</v>
+        <v>0.6060473083867665</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>52.90719881547128</v>
+        <v>52.9071988432067</v>
       </c>
       <c r="I79" s="2" t="n">
         <v>24.56568197014727</v>
@@ -4651,7 +4651,7 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.073334006420155</v>
+        <v>-0.0733340064922585</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4686,10 +4686,10 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>53.81515959084311</v>
+        <v>53.81515964639187</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>13.84047182844354</v>
+        <v>13.84047194563013</v>
       </c>
       <c r="J80" s="2" t="n">
         <v>1.062039272868343</v>
@@ -4704,7 +4704,7 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.0565367064258879</v>
+        <v>0.0565367065941359</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>50.88169667101549</v>
+        <v>50.88169658946583</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>20.72468759373304</v>
+        <v>20.72468754944252</v>
       </c>
       <c r="J81" s="2" t="n">
         <v>1.87377663670574</v>
@@ -4757,7 +4757,7 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.4572505732386115</v>
+        <v>0.457250573527024</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>56.30674929973411</v>
+        <v>56.30674916998967</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>24.89221609846834</v>
+        <v>24.89221614824548</v>
       </c>
       <c r="J82" s="2" t="n">
         <v>0.8994667110400992</v>
@@ -4810,7 +4810,7 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.1305014639213682</v>
+        <v>0.1305014639814581</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -4845,10 +4845,10 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>53.7975167718915</v>
+        <v>53.79751679844694</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>22.89439942013398</v>
+        <v>22.89439944180163</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>0.7268901292355514</v>
@@ -4863,7 +4863,7 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.6661421161884311</v>
+        <v>0.6661421161644121</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>505.995915129586</v>
+        <v>505.9959151295865</v>
       </c>
       <c r="E84" s="2" t="n">
         <v>22</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>49.25396667915797</v>
+        <v>49.25396670239081</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>19.41545018963921</v>
+        <v>19.41545019714489</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>1.01635673563096</v>
@@ -4916,7 +4916,7 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.0141926798356154</v>
+        <v>-0.0141926798596526</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>51.71062072464703</v>
+        <v>51.71062047167652</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>35.21966023274503</v>
+        <v>35.21966024212684</v>
       </c>
       <c r="J85" s="2" t="n">
         <v>0.8098892878360918</v>
@@ -4969,7 +4969,7 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.07739896359100989</v>
+        <v>-0.0773989636751288</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -5004,10 +5004,10 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>47.83492261916096</v>
+        <v>47.83492258134828</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>23.50421389900548</v>
+        <v>23.50421375544252</v>
       </c>
       <c r="J86" s="2" t="n">
         <v>0.6618224938727191</v>
@@ -5022,7 +5022,7 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.3793035891517287</v>
+        <v>0.3793035898487309</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>52.84512469167135</v>
+        <v>52.84512459974002</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>14.60166798283247</v>
+        <v>14.6016679915031</v>
       </c>
       <c r="J87" s="2" t="n">
         <v>1.059466512407928</v>
@@ -5075,7 +5075,7 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-7.80662020882265</v>
+        <v>-7.806620190796366</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -5110,10 +5110,10 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>47.49951923961035</v>
+        <v>47.49951914179265</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>20.79875287813569</v>
+        <v>20.79875293737864</v>
       </c>
       <c r="J88" s="2" t="n">
         <v>0.6016354168252437</v>
@@ -5128,7 +5128,7 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.0270356985146418</v>
+        <v>0.0270356986588507</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5163,10 +5163,10 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>53.32100332391303</v>
+        <v>53.32100329629315</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>21.17683131202534</v>
+        <v>21.17683129279094</v>
       </c>
       <c r="J89" s="2" t="n">
         <v>0.761545814045633</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0707033521180138</v>
+        <v>0.0707033520939801</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>59.21489929404957</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>32.27098590008472</v>
+        <v>32.27098592288814</v>
       </c>
       <c r="J90" s="2" t="n">
         <v>0.6386354321177182</v>
@@ -5234,7 +5234,7 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.8986595641653339</v>
+        <v>0.8986595642013833</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>43.58110168746114</v>
+        <v>43.58110112034333</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>7.016155832342461</v>
+        <v>7.016155816584914</v>
       </c>
       <c r="J91" s="2" t="n">
         <v>0.9947913848930594</v>
@@ -5287,7 +5287,7 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.484420131802695</v>
+        <v>0.4844201343263421</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -5322,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>55.47644705009844</v>
+        <v>55.47644705717184</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>34.9673418078572</v>
+        <v>34.96734195699217</v>
       </c>
       <c r="J92" s="2" t="n">
         <v>0.6096156755113674</v>
@@ -5340,7 +5340,7 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.2763031648220774</v>
+        <v>-0.2763031648100621</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>492.4506603805939</v>
+        <v>492.4506603805938</v>
       </c>
       <c r="E93" s="2" t="n">
         <v>145</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>55.4120738165611</v>
+        <v>55.41207364512731</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>9.205580455792774</v>
+        <v>9.205580483907449</v>
       </c>
       <c r="J93" s="2" t="n">
         <v>1.144478073142968</v>
@@ -5393,7 +5393,7 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.2424291764682229</v>
+        <v>0.2424291768287318</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>52.45909449784181</v>
+        <v>52.45909519936695</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>7.64788225775673</v>
+        <v>7.647881786928025</v>
       </c>
       <c r="J94" s="2" t="n">
         <v>0.9271753708803868</v>
@@ -5446,7 +5446,7 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.2731912464525083</v>
+        <v>0.2731912401975653</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>62.17757162792974</v>
+        <v>62.17757157118978</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>46.9583532367068</v>
+        <v>46.95835316441426</v>
       </c>
       <c r="J95" s="2" t="n">
         <v>0.3792163408687066</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>53.09614056169681</v>
+        <v>53.09614054150176</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>16.65716169399779</v>
+        <v>16.65716164241286</v>
       </c>
       <c r="J96" s="2" t="n">
         <v>0.8926934694292411</v>
@@ -5552,7 +5552,7 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.2869130200900882</v>
+        <v>-0.2869130199756713</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -5587,10 +5587,10 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>47.02380359601796</v>
+        <v>47.02380360461144</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>16.71361786633378</v>
+        <v>16.71361803313789</v>
       </c>
       <c r="J97" s="2" t="n">
         <v>0.8231411506543366</v>
@@ -5640,10 +5640,10 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>48.5166664226841</v>
+        <v>48.51666638683873</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>18.79959981856109</v>
+        <v>18.79959972696448</v>
       </c>
       <c r="J98" s="2" t="n">
         <v>0.5248180736331473</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.9747594299185294</v>
+        <v>-0.9747594293176528</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>48.36679689408254</v>
+        <v>48.36679672105063</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>17.18457785630737</v>
+        <v>17.18457784723421</v>
       </c>
       <c r="J99" s="2" t="n">
         <v>0.5804712086609459</v>
@@ -5732,7 +5732,7 @@
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>464.871960926219</v>
+        <v>464.8719609262204</v>
       </c>
       <c r="E100" s="2" t="n">
         <v>11.95</v>
@@ -5746,10 +5746,10 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>49.549328837681</v>
+        <v>49.54932878203615</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>20.12418272213539</v>
+        <v>20.12418271294484</v>
       </c>
       <c r="J100" s="2" t="n">
         <v>0.945037886320406</v>
@@ -5764,7 +5764,7 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.0170971759133008</v>
+        <v>0.0170971759373354</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -5799,10 +5799,10 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>49.00324704263437</v>
+        <v>49.00324703235216</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>8.379429745527119</v>
+        <v>8.379429845819059</v>
       </c>
       <c r="J101" s="2" t="n">
         <v>1.396623157661756</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.1082144257868788</v>
+        <v>0.1082144255465518</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>460.2945303113466</v>
+        <v>460.2945303113449</v>
       </c>
       <c r="E102" s="2" t="n">
         <v>28.75</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>59.34090288611333</v>
+        <v>59.34090276924749</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>23.55156548513825</v>
+        <v>23.55156552899965</v>
       </c>
       <c r="J102" s="2" t="n">
         <v>0.5475450310343187</v>
@@ -5870,7 +5870,7 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.3141820199559424</v>
+        <v>0.3141820201001457</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>460.230126878512</v>
+        <v>460.2301268785112</v>
       </c>
       <c r="E103" s="2" t="n">
         <v>56.2</v>
@@ -5905,10 +5905,10 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>55.92685399479157</v>
+        <v>55.92685394700637</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>34.78583659979661</v>
+        <v>34.78583659243922</v>
       </c>
       <c r="J103" s="2" t="n">
         <v>1.53776807320249</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.7852548994054619</v>
+        <v>0.7852548994535309</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5958,10 +5958,10 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>49.64686119396449</v>
+        <v>49.64686116617342</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>31.93821396706442</v>
+        <v>31.93821396966217</v>
       </c>
       <c r="J104" s="2" t="n">
         <v>1.121352560833478</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-50.06003076637901</v>
+        <v>-50.06003075676534</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>56.17518422716645</v>
+        <v>56.17518416309994</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>36.2686820528824</v>
+        <v>36.26868203981606</v>
       </c>
       <c r="J105" s="2" t="n">
         <v>0.5723853576086476</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.0600766125107972</v>
+        <v>-0.060076612354569</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6064,10 +6064,10 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>53.21460337175024</v>
+        <v>53.21460358781346</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>23.57428876650814</v>
+        <v>23.57428886440382</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>0.4652025587143022</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.0640996819886995</v>
+        <v>0.06409968178440539</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6117,10 +6117,10 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>52.85388230921383</v>
+        <v>52.85388229914581</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>35.78384243656978</v>
+        <v>35.78384245394895</v>
       </c>
       <c r="J107" s="2" t="n">
         <v>0.9766990117950652</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.4102932750830088</v>
+        <v>-0.4102932750709827</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>452.7422065098374</v>
+        <v>452.7422065098373</v>
       </c>
       <c r="E108" s="2" t="n">
         <v>41</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>48.50003851209726</v>
+        <v>48.5000385021291</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>28.65576091124708</v>
+        <v>28.65576099016513</v>
       </c>
       <c r="J108" s="2" t="n">
         <v>0.9151723080650735</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.4318290604532093</v>
+        <v>-0.4318290604411927</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>52.49301226413851</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>14.7130706178152</v>
+        <v>14.71307062465172</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>1.783247408392926</v>
@@ -6262,7 +6262,7 @@
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>451.7854771807596</v>
+        <v>451.7854771807627</v>
       </c>
       <c r="E110" s="2" t="n">
         <v>42</v>
@@ -6276,10 +6276,10 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>54.10668570577177</v>
+        <v>54.10668575375855</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>28.3756413108493</v>
+        <v>28.37564157643007</v>
       </c>
       <c r="J110" s="2" t="n">
         <v>0.4580482600235035</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.1019024551789341</v>
+        <v>0.1019024562965543</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>65.35183659691418</v>
+        <v>65.35183643223519</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>10.95146370675128</v>
+        <v>10.95146372612939</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>1.86080786961663</v>
@@ -6382,10 +6382,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>55.60466914185658</v>
+        <v>55.60466919185577</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>21.16544057927067</v>
+        <v>21.1654408298874</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>0.827162336283781</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.1422520715067775</v>
+        <v>0.1422520713145043</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6435,10 +6435,10 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>42.90534648227435</v>
+        <v>42.90534668989503</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>19.90857070935625</v>
+        <v>19.90857067660848</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>0.2162505386362421</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>1.762253460053931e-05</v>
+        <v>1.762250575947782e-05</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>46.18152187132195</v>
+        <v>46.18152181148513</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>26.44753587146588</v>
+        <v>26.44753587431189</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>1.309942484930338</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.0169778021233701</v>
+        <v>-0.0169778021113547</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>424.5889441014741</v>
+        <v>424.588944101468</v>
       </c>
       <c r="E115" s="2" t="n">
         <v>14.35</v>
@@ -6541,10 +6541,10 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>51.64164770042345</v>
+        <v>51.64164737487465</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>25.76107191306012</v>
+        <v>25.76107210576425</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>0.3692636336874076</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.0116000561511921</v>
+        <v>0.0116000562953998</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6594,10 +6594,10 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>42.94084512247801</v>
+        <v>42.9408450789814</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>23.22641773482401</v>
+        <v>23.22641780796808</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>0.4919888552491568</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.0367572093111242</v>
+        <v>-0.0367572092920542</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>417.4818300723596</v>
+        <v>417.4818300723597</v>
       </c>
       <c r="E117" s="2" t="n">
         <v>10.7</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>46.01555722433625</v>
+        <v>46.01555723789886</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>29.12462772780846</v>
+        <v>29.12462775823148</v>
       </c>
       <c r="J117" s="2" t="n">
         <v>0.4955901261101565</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.0744722432355666</v>
+        <v>-0.0744722432451798</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6700,10 +6700,10 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>54.76611144943276</v>
+        <v>54.76611159131468</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>28.79569561113157</v>
+        <v>28.79569555298213</v>
       </c>
       <c r="J118" s="2" t="n">
         <v>0.4948861319153823</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.0401146725569412</v>
+        <v>0.0401146724487896</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
@@ -6753,10 +6753,10 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>40.63013242993419</v>
+        <v>40.63013234023918</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>18.77808525515146</v>
+        <v>18.77808533242875</v>
       </c>
       <c r="J119" s="2" t="n">
         <v>1.552911778057812</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.6090891880069942</v>
+        <v>-0.6090891876464721</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>44.16480981978086</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>28.50889422658356</v>
+        <v>28.50889413067881</v>
       </c>
       <c r="J120" s="2" t="n">
         <v>0.8730358830063155</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.7681943949704977</v>
+        <v>0.768194394850326</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6859,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>46.09465741862643</v>
+        <v>46.09465736814536</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>14.85180711183099</v>
+        <v>14.85180706164256</v>
       </c>
       <c r="J121" s="2" t="n">
         <v>0.9013174907501434</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-1.538698878218225</v>
+        <v>-1.538698878338388</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6912,10 +6912,10 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>46.52478853033107</v>
+        <v>46.52478851704559</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>20.69248907956834</v>
+        <v>20.69248915042018</v>
       </c>
       <c r="J122" s="2" t="n">
         <v>0.791986819447853</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>47.10699735776388</v>
+        <v>47.10699734169133</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>24.45153331661906</v>
+        <v>24.45153328872035</v>
       </c>
       <c r="J123" s="2" t="n">
         <v>0.5056415748598001</v>
@@ -7018,10 +7018,10 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>49.25283321809001</v>
+        <v>49.25283311779656</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>19.86471323857404</v>
+        <v>19.86471313001198</v>
       </c>
       <c r="J124" s="2" t="n">
         <v>0.2881659334399506</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.1616495030647085</v>
+        <v>-0.161649502992592</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7071,10 +7071,10 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>31.63601090960995</v>
+        <v>31.63601084513623</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>31.4102081648634</v>
+        <v>31.41020844582553</v>
       </c>
       <c r="J125" s="2" t="n">
         <v>0.5751414246013501</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.408167502270476</v>
+        <v>-0.4081675021863549</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>47.87462814855186</v>
+        <v>47.87462810868461</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>23.17534125293978</v>
+        <v>23.1753412621586</v>
       </c>
       <c r="J126" s="2" t="n">
         <v>0.2002691929731018</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.1169331920676274</v>
+        <v>-0.1169331920556107</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>381.2287594195303</v>
+        <v>381.2287594195308</v>
       </c>
       <c r="E127" s="2" t="n">
         <v>37.85</v>
@@ -7177,10 +7177,10 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>46.84474533701404</v>
+        <v>46.84474531502322</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>18.27934077422409</v>
+        <v>18.27934076745492</v>
       </c>
       <c r="J127" s="2" t="n">
         <v>0.6901614062294043</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.009092749341966499</v>
+        <v>-0.009092749293902601</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>376.5904118949337</v>
+        <v>376.5904118949338</v>
       </c>
       <c r="E128" s="2" t="n">
         <v>16.85</v>
@@ -7230,10 +7230,10 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>47.85978791132083</v>
+        <v>47.85978784828288</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>20.30129310536552</v>
+        <v>20.30129312838475</v>
       </c>
       <c r="J128" s="2" t="n">
         <v>0.3364516421504003</v>
@@ -7248,7 +7248,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-0.064504257922676</v>
+        <v>-0.06450425789864241</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>376.3299980343433</v>
+        <v>376.3299980343435</v>
       </c>
       <c r="E129" s="2" t="n">
         <v>10.45</v>
@@ -7283,10 +7283,10 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>45.44046114886734</v>
+        <v>45.44046081989905</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>25.7607471319477</v>
+        <v>25.76074720221735</v>
       </c>
       <c r="J129" s="2" t="n">
         <v>0.5175032938158998</v>
@@ -7301,7 +7301,7 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>0.0315021139610777</v>
+        <v>0.0315021139971298</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>374.9417959317135</v>
+        <v>374.9417959317134</v>
       </c>
       <c r="E130" s="2" t="n">
         <v>22</v>
@@ -7336,10 +7336,10 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>46.99881774070453</v>
+        <v>46.9988176411249</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>20.04601166265961</v>
+        <v>20.04601170457744</v>
       </c>
       <c r="J130" s="2" t="n">
         <v>1.243893123940176</v>
@@ -7354,7 +7354,7 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>-0.0490579157081774</v>
+        <v>-0.0490579157201949</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
@@ -7389,10 +7389,10 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>49.64988845581865</v>
+        <v>49.64988837170556</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>23.94359157621871</v>
+        <v>23.94359158802691</v>
       </c>
       <c r="J131" s="2" t="n">
         <v>0.5719317913122453</v>
@@ -7407,7 +7407,7 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>-1.096542335296628</v>
+        <v>-1.096542335320654</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>369.4950536815604</v>
+        <v>369.9446213139699</v>
       </c>
       <c r="E132" s="2" t="n">
         <v>56.6</v>
@@ -7460,7 +7460,7 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>0.0647090202583521</v>
+        <v>0.06111662742939</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
@@ -7495,10 +7495,10 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>45.70441340927634</v>
+        <v>45.70441309230181</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>23.57900654020676</v>
+        <v>23.57900657333477</v>
       </c>
       <c r="J133" s="2" t="n">
         <v>0.5318095837324148</v>
@@ -7513,7 +7513,7 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>-0.0014496627535413</v>
+        <v>-0.001449662056539</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
@@ -7548,10 +7548,10 @@
         <v>0</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>45.2799471041786</v>
+        <v>45.27994701478874</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>9.584815559577134</v>
+        <v>9.584815565897523</v>
       </c>
       <c r="J134" s="2" t="n">
         <v>0.6575764786511968</v>
@@ -7566,7 +7566,7 @@
         <v>-1</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>-0.0624611080563216</v>
+        <v>-0.0624611080082451</v>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
@@ -7601,10 +7601,10 @@
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>44.74711933266114</v>
+        <v>44.74711930566704</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>10.21486251442942</v>
+        <v>10.21486256120441</v>
       </c>
       <c r="J135" s="2" t="n">
         <v>0.1464165753032451</v>
@@ -7619,7 +7619,7 @@
         <v>-1</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>-0.064059314643648</v>
+        <v>-0.06405931461961099</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
@@ -7654,10 +7654,10 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>48.74593356028227</v>
+        <v>48.74593356818546</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>16.33093596990988</v>
+        <v>16.33093612002812</v>
       </c>
       <c r="J136" s="2" t="n">
         <v>0.6545179807884831</v>
@@ -7672,7 +7672,7 @@
         <v>-1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>0.09749231169672901</v>
+        <v>0.0974923116246196</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
@@ -7707,10 +7707,10 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>49.264046643117</v>
+        <v>49.26404662425577</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>10.07539446390502</v>
+        <v>10.07539444163571</v>
       </c>
       <c r="J137" s="2" t="n">
         <v>0.4974322078050959</v>
@@ -7725,7 +7725,7 @@
         <v>-1</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>0.0332505910196279</v>
+        <v>0.0332505910316452</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>41.27101716752522</v>
+        <v>41.27101699658015</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>13.13542611792548</v>
+        <v>13.13542600643899</v>
       </c>
       <c r="J138" s="2" t="n">
         <v>0.6748515247649027</v>
@@ -7813,10 +7813,10 @@
         <v>0</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>45.82778747752892</v>
+        <v>45.8277873362467</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>19.92889072873198</v>
+        <v>19.92889075026333</v>
       </c>
       <c r="J139" s="2" t="n">
         <v>0.5790078569279881</v>
@@ -7831,7 +7831,7 @@
         <v>-1</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>-0.0552716326695025</v>
+        <v>-0.0552716325949959</v>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v/>
       </c>
       <c r="D140" s="2" t="n">
-        <v>345.5520037969901</v>
+        <v>345.5520037969903</v>
       </c>
       <c r="E140" s="2" t="n">
         <v>267</v>
@@ -7866,10 +7866,10 @@
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>44.87959502059068</v>
+        <v>44.87959501668781</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>15.4080971478286</v>
+        <v>15.40809717973299</v>
       </c>
       <c r="J140" s="2" t="n">
         <v>0.6052563069198605</v>
@@ -7884,7 +7884,7 @@
         <v>-1</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>-2.88902547794044</v>
+        <v>-2.889025477988481</v>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
@@ -7919,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>50.10933025308419</v>
+        <v>50.10933030353609</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>28.42871866090482</v>
+        <v>28.42871857207492</v>
       </c>
       <c r="J141" s="2" t="n">
         <v>0.3229693117282342</v>
@@ -7937,7 +7937,7 @@
         <v>-1</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>0.0252017607462529</v>
+        <v>0.0252017607342353</v>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v/>
       </c>
       <c r="D142" s="2" t="n">
-        <v>337.5286951206259</v>
+        <v>337.5286951206256</v>
       </c>
       <c r="E142" s="2" t="n">
         <v>12.1</v>
@@ -7972,10 +7972,10 @@
         <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>33.4536256264615</v>
+        <v>33.45362549174834</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>28.65141202372292</v>
+        <v>28.65141184910174</v>
       </c>
       <c r="J142" s="2" t="n">
         <v>1.053047595234831</v>
@@ -7990,7 +7990,7 @@
         <v>-1</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>-0.0748631944264095</v>
+        <v>-0.0748631944143917</v>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v/>
       </c>
       <c r="D143" s="2" t="n">
-        <v>337.4215190603497</v>
+        <v>337.4215190603489</v>
       </c>
       <c r="E143" s="2" t="n">
         <v>18.75</v>
@@ -8025,10 +8025,10 @@
         <v>0</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>53.41203561687751</v>
+        <v>53.41203548576805</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>32.90322169167846</v>
+        <v>32.90322171707782</v>
       </c>
       <c r="J143" s="2" t="n">
         <v>0.3527219224086896</v>
@@ -8043,7 +8043,7 @@
         <v>-1</v>
       </c>
       <c r="N143" s="2" t="n">
-        <v>-0.0392894813793341</v>
+        <v>-0.0392894809947804</v>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
@@ -8078,10 +8078,10 @@
         <v>0</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>37.92353760001554</v>
+        <v>37.92353763015598</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>13.73664498515738</v>
+        <v>13.73664505727015</v>
       </c>
       <c r="J144" s="2" t="n">
         <v>0.6365377550577058</v>
@@ -8096,7 +8096,7 @@
         <v>-1</v>
       </c>
       <c r="N144" s="2" t="n">
-        <v>0.1748890027320677</v>
+        <v>0.1748890025758408</v>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v/>
       </c>
       <c r="D145" s="2" t="n">
-        <v>330.4135262659152</v>
+        <v>330.4135262659158</v>
       </c>
       <c r="E145" s="2" t="n">
         <v>15.6</v>
@@ -8131,10 +8131,10 @@
         <v>0</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>43.35201262673599</v>
+        <v>43.35201256746664</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>25.07439165391062</v>
+        <v>25.07439169137677</v>
       </c>
       <c r="J145" s="2" t="n">
         <v>1.063786777092382</v>
@@ -8149,7 +8149,7 @@
         <v>-1</v>
       </c>
       <c r="N145" s="2" t="n">
-        <v>-0.0867240411357398</v>
+        <v>-0.0867240410976</v>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v/>
       </c>
       <c r="D146" s="2" t="n">
-        <v>326.6573301834262</v>
+        <v>326.6573301834156</v>
       </c>
       <c r="E146" s="2" t="n">
         <v>24.15</v>
@@ -8184,10 +8184,10 @@
         <v>0</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>53.90377220189234</v>
+        <v>53.90377219435174</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>24.59669890955134</v>
+        <v>24.59669891204408</v>
       </c>
       <c r="J146" s="2" t="n">
         <v>0.2749650480660545</v>
@@ -8202,7 +8202,7 @@
         <v>-1</v>
       </c>
       <c r="N146" s="2" t="n">
-        <v>0.198905685075289</v>
+        <v>0.1989056850632736</v>
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>44.94649975044322</v>
+        <v>44.94649975651498</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>20.91348416530726</v>
+        <v>20.91348409129015</v>
       </c>
       <c r="J147" s="2" t="n">
         <v>0.8450869927082509</v>
@@ -8255,7 +8255,7 @@
         <v>-1</v>
       </c>
       <c r="N147" s="2" t="n">
-        <v>-0.2968914473386272</v>
+        <v>-0.296891447086264</v>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
@@ -8290,10 +8290,10 @@
         <v>0</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>50.46904839299133</v>
+        <v>50.46904827761252</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>16.19861502252649</v>
+        <v>16.19861519796431</v>
       </c>
       <c r="J148" s="2" t="n">
         <v>0.8113257395164939</v>
@@ -8308,7 +8308,7 @@
         <v>-1</v>
       </c>
       <c r="N148" s="2" t="n">
-        <v>-0.0156889234172058</v>
+        <v>-0.0156889233210587</v>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
@@ -8343,10 +8343,10 @@
         <v>0</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>50.55498048003523</v>
+        <v>50.55498022470951</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>17.91736238238053</v>
+        <v>17.91736250827668</v>
       </c>
       <c r="J149" s="2" t="n">
         <v>0.7170181032339032</v>
@@ -8361,7 +8361,7 @@
         <v>-1</v>
       </c>
       <c r="N149" s="2" t="n">
-        <v>0.0086810712103045</v>
+        <v>0.0086810713545109</v>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>47.77533817284539</v>
+        <v>47.77533876630262</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>8.373727145370323</v>
+        <v>8.373727184926127</v>
       </c>
       <c r="J150" s="2" t="n">
         <v>0.7006248934929467</v>
@@ -8414,7 +8414,7 @@
         <v>-1</v>
       </c>
       <c r="N150" s="2" t="n">
-        <v>0.036872413458611</v>
+        <v>0.0368724135066796</v>
       </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
@@ -8449,10 +8449,10 @@
         <v>0</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>43.19834772361923</v>
+        <v>43.19834763956244</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>11.46690331991395</v>
+        <v>11.46690339937756</v>
       </c>
       <c r="J151" s="2" t="n">
         <v>0.3635667759315786</v>
@@ -8467,7 +8467,7 @@
         <v>-1</v>
       </c>
       <c r="N151" s="2" t="n">
-        <v>-0.0765600050783226</v>
+        <v>-0.07656000500622</v>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v/>
       </c>
       <c r="D152" s="2" t="n">
-        <v>308.6131081855573</v>
+        <v>308.613108185556</v>
       </c>
       <c r="E152" s="2" t="n">
         <v>38.1</v>
@@ -8502,10 +8502,10 @@
         <v>0</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>45.18819183547164</v>
+        <v>45.18819180728408</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>17.35696265334143</v>
+        <v>17.35696300123087</v>
       </c>
       <c r="J152" s="2" t="n">
         <v>0.7332246997543435</v>
@@ -8520,7 +8520,7 @@
         <v>-1</v>
       </c>
       <c r="N152" s="2" t="n">
-        <v>0.1320164226479434</v>
+        <v>0.1320164227681171</v>
       </c>
       <c r="O152" s="2" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         <v/>
       </c>
       <c r="D153" s="2" t="n">
-        <v>307.6159440582486</v>
+        <v>307.6159440582487</v>
       </c>
       <c r="E153" s="2" t="n">
         <v>120.5</v>
@@ -8555,10 +8555,10 @@
         <v>0</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>50.52108796203723</v>
+        <v>50.52108803132957</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>17.09636786901175</v>
+        <v>17.09636778492724</v>
       </c>
       <c r="J153" s="2" t="n">
         <v>0.3994530956789767</v>
@@ -8573,7 +8573,7 @@
         <v>-1</v>
       </c>
       <c r="N153" s="2" t="n">
-        <v>0.688668354204685</v>
+        <v>0.6886683540845002</v>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
@@ -8608,10 +8608,10 @@
         <v>0</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>51.84113304400449</v>
+        <v>51.84113301347019</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>17.22070858492274</v>
+        <v>17.22070861130679</v>
       </c>
       <c r="J154" s="2" t="n">
         <v>0.6534980418214584</v>
@@ -8626,7 +8626,7 @@
         <v>-1</v>
       </c>
       <c r="N154" s="2" t="n">
-        <v>0.3648375152578256</v>
+        <v>0.3648375152097536</v>
       </c>
       <c r="O154" s="2" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>54.24517972957368</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>24.421082125646</v>
+        <v>24.42108222015874</v>
       </c>
       <c r="J155" s="2" t="n">
         <v>0.2083504488620704</v>
@@ -8679,7 +8679,7 @@
         <v>-1</v>
       </c>
       <c r="N155" s="2" t="n">
-        <v>0.0389564606404527</v>
+        <v>0.0389564606164199</v>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v/>
       </c>
       <c r="D156" s="2" t="n">
-        <v>298.1562946973851</v>
+        <v>298.1562946973859</v>
       </c>
       <c r="E156" s="2" t="n">
         <v>5.76</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>50.37029246629105</v>
+        <v>50.37029237924899</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>13.54600164110626</v>
+        <v>13.54600163500595</v>
       </c>
       <c r="J156" s="2" t="n">
         <v>0.4260448494178075</v>
@@ -8732,7 +8732,7 @@
         <v>-1</v>
       </c>
       <c r="N156" s="2" t="n">
-        <v>-0.0100050991020968</v>
+        <v>-0.0100050991189214</v>
       </c>
       <c r="O156" s="2" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v/>
       </c>
       <c r="D157" s="2" t="n">
-        <v>297.8945731326065</v>
+        <v>297.8945731326063</v>
       </c>
       <c r="E157" s="2" t="n">
         <v>195.5</v>
@@ -8767,10 +8767,10 @@
         <v>0</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>31.8417656794298</v>
+        <v>31.84176574763836</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>17.97810273748159</v>
+        <v>17.97810275593289</v>
       </c>
       <c r="J157" s="2" t="n">
         <v>0.9243291834187418</v>
@@ -8785,7 +8785,7 @@
         <v>-1</v>
       </c>
       <c r="N157" s="2" t="n">
-        <v>-1.430265852289448</v>
+        <v>-1.430265853250846</v>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
@@ -8820,10 +8820,10 @@
         <v>0</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>35.78232882068748</v>
+        <v>35.78232873648869</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>9.855236322187489</v>
+        <v>9.855236414594795</v>
       </c>
       <c r="J158" s="2" t="n">
         <v>1.049942804899381</v>
@@ -8838,7 +8838,7 @@
         <v>-1</v>
       </c>
       <c r="N158" s="2" t="n">
-        <v>0.0229671210153838</v>
+        <v>0.0229671209913471</v>
       </c>
       <c r="O158" s="2" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v/>
       </c>
       <c r="D159" s="2" t="n">
-        <v>296.4117179003796</v>
+        <v>296.4117179003788</v>
       </c>
       <c r="E159" s="2" t="n">
         <v>22.75</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>36.3224466875572</v>
+        <v>36.32244611452288</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>28.77270565898539</v>
+        <v>28.77270553513</v>
       </c>
       <c r="J159" s="2" t="n">
         <v>1.149047968989999</v>
@@ -8891,7 +8891,7 @@
         <v>-1</v>
       </c>
       <c r="N159" s="2" t="n">
-        <v>0.032993599289312</v>
+        <v>0.0329935995777264</v>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v/>
       </c>
       <c r="D160" s="2" t="n">
-        <v>287.7919663318524</v>
+        <v>287.7919663318515</v>
       </c>
       <c r="E160" s="2" t="n">
         <v>51.7</v>
@@ -8926,10 +8926,10 @@
         <v>0</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>41.04974446622001</v>
+        <v>41.0497444303992</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>16.92916595429906</v>
+        <v>16.92916597531594</v>
       </c>
       <c r="J160" s="2" t="n">
         <v>0.9659409054300599</v>
@@ -8944,7 +8944,7 @@
         <v>-1</v>
       </c>
       <c r="N160" s="2" t="n">
-        <v>0.0289227826515099</v>
+        <v>0.0289227826274748</v>
       </c>
       <c r="O160" s="2" t="inlineStr">
         <is>
@@ -8979,10 +8979,10 @@
         <v>0</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>51.7517176577799</v>
+        <v>51.7517177649794</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>17.36521807215324</v>
+        <v>17.36521812771699</v>
       </c>
       <c r="J161" s="2" t="n">
         <v>0.4183082172547885</v>
@@ -8997,7 +8997,7 @@
         <v>-1</v>
       </c>
       <c r="N161" s="2" t="n">
-        <v>0.0616364284177239</v>
+        <v>0.0616364283696568</v>
       </c>
       <c r="O161" s="2" t="inlineStr">
         <is>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>22.46845405141066</v>
+        <v>22.46845402081642</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>30.80158401380417</v>
+        <v>30.80158405950302</v>
       </c>
       <c r="J162" s="2" t="n">
         <v>0.7421047831587415</v>
@@ -9050,7 +9050,7 @@
         <v>-1</v>
       </c>
       <c r="N162" s="2" t="n">
-        <v>-0.3411836212859775</v>
+        <v>-0.3411836212619411</v>
       </c>
       <c r="O162" s="2" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         <v/>
       </c>
       <c r="D163" s="2" t="n">
-        <v>282.6913520346985</v>
+        <v>282.6913520347001</v>
       </c>
       <c r="E163" s="2" t="n">
         <v>38.9</v>
@@ -9085,10 +9085,10 @@
         <v>0</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>52.06862570831957</v>
+        <v>52.06862554769987</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>16.19468911364697</v>
+        <v>16.19468919118451</v>
       </c>
       <c r="J163" s="2" t="n">
         <v>0.3904601636818935</v>
@@ -9103,7 +9103,7 @@
         <v>-1</v>
       </c>
       <c r="N163" s="2" t="n">
-        <v>-0.0064389871172897</v>
+        <v>-0.0064389871653603</v>
       </c>
       <c r="O163" s="2" t="inlineStr">
         <is>
@@ -9138,10 +9138,10 @@
         <v>0</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>40.18550134570779</v>
+        <v>40.18550130072871</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>13.39657598634548</v>
+        <v>13.39657590290055</v>
       </c>
       <c r="J164" s="2" t="n">
         <v>0.4884164567734902</v>
@@ -9156,7 +9156,7 @@
         <v>-1</v>
       </c>
       <c r="N164" s="2" t="n">
-        <v>0.1101323291353502</v>
+        <v>0.1101323290151774</v>
       </c>
       <c r="O164" s="2" t="inlineStr">
         <is>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>51.40524781900758</v>
+        <v>51.40524780672871</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>20.62536602029079</v>
+        <v>20.62536602484119</v>
       </c>
       <c r="J165" s="2" t="n">
         <v>0.4625664133366969</v>
@@ -9230,7 +9230,7 @@
         <v/>
       </c>
       <c r="D166" s="2" t="n">
-        <v>281.9725361765377</v>
+        <v>281.9725361765376</v>
       </c>
       <c r="E166" s="2" t="n">
         <v>11.6</v>
@@ -9244,10 +9244,10 @@
         <v>0</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>51.82604970848711</v>
+        <v>51.82604948692808</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>18.97074597603515</v>
+        <v>18.97074602700987</v>
       </c>
       <c r="J166" s="2" t="n">
         <v>0.659036611911667</v>
@@ -9262,7 +9262,7 @@
         <v>-1</v>
       </c>
       <c r="N166" s="2" t="n">
-        <v>0.0163652028117058</v>
+        <v>0.016365202823724</v>
       </c>
       <c r="O166" s="2" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         <v/>
       </c>
       <c r="D167" s="2" t="n">
-        <v>278.0620648698326</v>
+        <v>278.0620648698327</v>
       </c>
       <c r="E167" s="2" t="n">
         <v>20.15</v>
@@ -9297,10 +9297,10 @@
         <v>0</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>46.11181643778363</v>
+        <v>46.11181626486205</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>7.989331142245902</v>
+        <v>7.989331248718733</v>
       </c>
       <c r="J167" s="2" t="n">
         <v>0.5630234816652252</v>
@@ -9315,7 +9315,7 @@
         <v>-1</v>
       </c>
       <c r="N167" s="2" t="n">
-        <v>0.0130193772520277</v>
+        <v>0.0130193773000965</v>
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>45.08580910514147</v>
+        <v>45.08580898285321</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>11.62788302064551</v>
+        <v>11.62788306177983</v>
       </c>
       <c r="J168" s="2" t="n">
         <v>0.7580132154298453</v>
@@ -9403,10 +9403,10 @@
         <v>0</v>
       </c>
       <c r="H169" s="2" t="n">
-        <v>36.67479935113923</v>
+        <v>36.67479978122417</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>10.93404828734326</v>
+        <v>10.93404822539545</v>
       </c>
       <c r="J169" s="2" t="n">
         <v>2.885710891427134</v>
@@ -9421,7 +9421,7 @@
         <v>-1</v>
       </c>
       <c r="N169" s="2" t="n">
-        <v>-0.0166055571589173</v>
+        <v>-0.0166055572670733</v>
       </c>
       <c r="O169" s="2" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         <v>51.58697723314374</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>28.22452296314442</v>
+        <v>28.22452303839632</v>
       </c>
       <c r="J170" s="2" t="n">
         <v>0.584491119334033</v>
@@ -9474,7 +9474,7 @@
         <v>-1</v>
       </c>
       <c r="N170" s="2" t="n">
-        <v>-0.0436006678143792</v>
+        <v>-0.0436006677422759</v>
       </c>
       <c r="O170" s="2" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>0</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>44.47912264063589</v>
+        <v>44.47912268176911</v>
       </c>
       <c r="I171" s="2" t="n">
         <v>19.30496152274933</v>
@@ -9527,7 +9527,7 @@
         <v>-1</v>
       </c>
       <c r="N171" s="2" t="n">
-        <v>-0.1529997778864005</v>
+        <v>-0.1529997779344708</v>
       </c>
       <c r="O171" s="2" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>45.86299085927416</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>17.54829545648398</v>
+        <v>17.54829552767041</v>
       </c>
       <c r="J172" s="2" t="n">
         <v>0.2852960787354688</v>
@@ -9615,10 +9615,10 @@
         <v>0</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>34.77894208731342</v>
+        <v>34.77894184666981</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>20.06164401361689</v>
+        <v>20.0616442465546</v>
       </c>
       <c r="J173" s="2" t="n">
         <v>0.2668711513159156</v>
@@ -9633,7 +9633,7 @@
         <v>-1</v>
       </c>
       <c r="N173" s="2" t="n">
-        <v>-0.0512474128019485</v>
+        <v>-0.051247412645727</v>
       </c>
       <c r="O173" s="2" t="inlineStr">
         <is>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="H174" s="2" t="n">
-        <v>48.11205697165254</v>
+        <v>48.11205673498064</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>23.78975874929501</v>
+        <v>23.7897587599146</v>
       </c>
       <c r="J174" s="2" t="n">
         <v>0.2826343236088637</v>
@@ -9686,7 +9686,7 @@
         <v>-1</v>
       </c>
       <c r="N174" s="2" t="n">
-        <v>-0.1347734926680349</v>
+        <v>-0.1347734924517222</v>
       </c>
       <c r="O174" s="2" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v/>
       </c>
       <c r="D175" s="2" t="n">
-        <v>255.6791549455241</v>
+        <v>255.6791549455249</v>
       </c>
       <c r="E175" s="2" t="n">
         <v>77</v>
@@ -9721,10 +9721,10 @@
         <v>0</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>47.02759165555731</v>
+        <v>47.02759140097479</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>18.91524798590038</v>
+        <v>18.91524800817447</v>
       </c>
       <c r="J175" s="2" t="n">
         <v>0.3943189530515097</v>
@@ -9739,7 +9739,7 @@
         <v>-1</v>
       </c>
       <c r="N175" s="2" t="n">
-        <v>0.1092732748678958</v>
+        <v>0.1092732749880761</v>
       </c>
       <c r="O175" s="2" t="inlineStr">
         <is>
@@ -9774,10 +9774,10 @@
         <v>0</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>44.32115330028908</v>
+        <v>44.32115310226741</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>9.928065437020054</v>
+        <v>9.928065468010542</v>
       </c>
       <c r="J176" s="2" t="n">
         <v>1.010905389554014</v>
@@ -9792,7 +9792,7 @@
         <v>-1</v>
       </c>
       <c r="N176" s="2" t="n">
-        <v>-0.0231343795053133</v>
+        <v>-0.0231343794572425</v>
       </c>
       <c r="O176" s="2" t="inlineStr">
         <is>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>45.16735938424264</v>
+        <v>45.16735947100898</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>22.37044857349421</v>
+        <v>22.37044858429203</v>
       </c>
       <c r="J177" s="2" t="n">
         <v>1.129945545010763</v>
@@ -9845,7 +9845,7 @@
         <v>-1</v>
       </c>
       <c r="N177" s="2" t="n">
-        <v>0.0244014942797978</v>
+        <v>0.0244014942557645</v>
       </c>
       <c r="O177" s="2" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
         <v/>
       </c>
       <c r="D178" s="2" t="n">
-        <v>246.8076686467858</v>
+        <v>246.807668646786</v>
       </c>
       <c r="E178" s="2" t="n">
         <v>13.75</v>
@@ -9880,10 +9880,10 @@
         <v>0</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>44.72746286048744</v>
+        <v>44.72746277173274</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>11.93196269953143</v>
+        <v>11.9319625736858</v>
       </c>
       <c r="J178" s="2" t="n">
         <v>0.9274814593020974</v>
@@ -9898,7 +9898,7 @@
         <v>-1</v>
       </c>
       <c r="N178" s="2" t="n">
-        <v>-0.0317870008820729</v>
+        <v>-0.0317870009061069</v>
       </c>
       <c r="O178" s="2" t="inlineStr">
         <is>
@@ -9933,10 +9933,10 @@
         <v>0</v>
       </c>
       <c r="H179" s="2" t="n">
-        <v>41.43662977078607</v>
+        <v>41.43662956797419</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>14.30774757701548</v>
+        <v>14.30774747550462</v>
       </c>
       <c r="J179" s="2" t="n">
         <v>1.540331220968467</v>
@@ -9951,7 +9951,7 @@
         <v>-1</v>
       </c>
       <c r="N179" s="2" t="n">
-        <v>-0.0106089548533502</v>
+        <v>-0.0106089548653704</v>
       </c>
       <c r="O179" s="2" t="inlineStr">
         <is>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="H180" s="2" t="n">
-        <v>45.05189765417538</v>
+        <v>45.05189782572439</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>30.41767979284721</v>
+        <v>30.41767978802838</v>
       </c>
       <c r="J180" s="2" t="n">
         <v>0.5297246999504828</v>
@@ -10004,7 +10004,7 @@
         <v>-1</v>
       </c>
       <c r="N180" s="2" t="n">
-        <v>0.0490050518680907</v>
+        <v>0.0490050519522107</v>
       </c>
       <c r="O180" s="2" t="inlineStr">
         <is>
@@ -10039,10 +10039,10 @@
         <v>0</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>47.07459582592374</v>
+        <v>47.07459528494869</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>14.90476592823938</v>
+        <v>14.90476614145295</v>
       </c>
       <c r="J181" s="2" t="n">
         <v>0.8528506316383421</v>
@@ -10057,7 +10057,7 @@
         <v>-1</v>
       </c>
       <c r="N181" s="2" t="n">
-        <v>0.2582819935198598</v>
+        <v>0.2582819941808159</v>
       </c>
       <c r="O181" s="2" t="inlineStr">
         <is>
@@ -10092,10 +10092,10 @@
         <v>0</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>45.24615443665581</v>
+        <v>45.24615434819665</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>17.31208707706766</v>
+        <v>17.31208713591426</v>
       </c>
       <c r="J182" s="2" t="n">
         <v>1.290423063201337</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>36.3740481127867</v>
+        <v>36.37404778258049</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>12.21362936009799</v>
+        <v>12.21362942212674</v>
       </c>
       <c r="J183" s="2" t="n">
         <v>0.6233960391909781</v>
@@ -10163,7 +10163,7 @@
         <v>-1</v>
       </c>
       <c r="N183" s="2" t="n">
-        <v>-0.0089243579880759</v>
+        <v>-0.008924357927990199</v>
       </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
@@ -10184,7 +10184,7 @@
         <v/>
       </c>
       <c r="D184" s="2" t="n">
-        <v>232.7378641290976</v>
+        <v>232.737864129098</v>
       </c>
       <c r="E184" s="2" t="n">
         <v>8.25</v>
@@ -10198,10 +10198,10 @@
         <v>0</v>
       </c>
       <c r="H184" s="2" t="n">
-        <v>40.54580255516905</v>
+        <v>40.54580261675078</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>13.13722243130513</v>
+        <v>13.13722244237022</v>
       </c>
       <c r="J184" s="2" t="n">
         <v>1.351310000819434</v>
@@ -10237,7 +10237,7 @@
         <v/>
       </c>
       <c r="D185" s="2" t="n">
-        <v>230.8509204089653</v>
+        <v>230.8509204089655</v>
       </c>
       <c r="E185" s="2" t="n">
         <v>12.95</v>
@@ -10251,10 +10251,10 @@
         <v>0</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>38.86628271959582</v>
+        <v>38.86628255869219</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>16.7440418527978</v>
+        <v>16.74404185279781</v>
       </c>
       <c r="J185" s="2" t="n">
         <v>0.3366570056873748</v>
@@ -10269,7 +10269,7 @@
         <v>-1</v>
       </c>
       <c r="N185" s="2" t="n">
-        <v>-0.0582728065280729</v>
+        <v>-0.058272806480004</v>
       </c>
       <c r="O185" s="2" t="inlineStr">
         <is>
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="H186" s="2" t="n">
-        <v>32.50002505480157</v>
+        <v>32.50002510027343</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>19.68205005963125</v>
+        <v>19.68205010379633</v>
       </c>
       <c r="J186" s="2" t="n">
         <v>1.360649646660604</v>
@@ -10322,7 +10322,7 @@
         <v>-1</v>
       </c>
       <c r="N186" s="2" t="n">
-        <v>-0.1310030409927106</v>
+        <v>-0.1310030409686763</v>
       </c>
       <c r="O186" s="2" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>35.2883070518163</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>36.24321376668698</v>
+        <v>36.24321376319037</v>
       </c>
       <c r="J187" s="2" t="n">
         <v>1.05516098499058</v>
@@ -10375,7 +10375,7 @@
         <v>-1</v>
       </c>
       <c r="N187" s="2" t="n">
-        <v>0.0082665782828968</v>
+        <v>0.008266578294912799</v>
       </c>
       <c r="O187" s="2" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v/>
       </c>
       <c r="D188" s="2" t="n">
-        <v>218.8638051324496</v>
+        <v>218.86380513245</v>
       </c>
       <c r="E188" s="2" t="n">
         <v>32.05</v>
@@ -10410,10 +10410,10 @@
         <v>0</v>
       </c>
       <c r="H188" s="2" t="n">
-        <v>28.66555793010052</v>
+        <v>28.66555695756182</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>11.53641673490234</v>
+        <v>11.53641744446682</v>
       </c>
       <c r="J188" s="2" t="n">
         <v>1.903878369971426</v>
@@ -10428,7 +10428,7 @@
         <v>-1</v>
       </c>
       <c r="N188" s="2" t="n">
-        <v>-0.1108329843868515</v>
+        <v>-0.1108329832812593</v>
       </c>
       <c r="O188" s="2" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v/>
       </c>
       <c r="D189" s="2" t="n">
-        <v>217.7837154034942</v>
+        <v>217.7837154034943</v>
       </c>
       <c r="E189" s="2" t="n">
         <v>16.65</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="H189" s="2" t="n">
-        <v>42.53502025816484</v>
+        <v>42.53502001150631</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>13.33155953290461</v>
+        <v>13.33155961470176</v>
       </c>
       <c r="J189" s="2" t="n">
         <v>0.5798636891061452</v>
@@ -10481,7 +10481,7 @@
         <v>-1</v>
       </c>
       <c r="N189" s="2" t="n">
-        <v>-0.0222041646788891</v>
+        <v>-0.0222041646668701</v>
       </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
@@ -10516,10 +10516,10 @@
         <v>0</v>
       </c>
       <c r="H190" s="2" t="n">
-        <v>46.14590280355096</v>
+        <v>46.14590275695631</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>18.40836485540679</v>
+        <v>18.4083647669096</v>
       </c>
       <c r="J190" s="2" t="n">
         <v>0.4936213683917115</v>
@@ -10534,7 +10534,7 @@
         <v>-1</v>
       </c>
       <c r="N190" s="2" t="n">
-        <v>-0.0116600753580954</v>
+        <v>-0.0116600753460782</v>
       </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
@@ -10555,7 +10555,7 @@
         <v/>
       </c>
       <c r="D191" s="2" t="n">
-        <v>215.8831265705066</v>
+        <v>215.8831265705067</v>
       </c>
       <c r="E191" s="2" t="n">
         <v>77.40000000000001</v>
@@ -10569,10 +10569,10 @@
         <v>0</v>
       </c>
       <c r="H191" s="2" t="n">
-        <v>29.6106485253352</v>
+        <v>29.61064854077557</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>14.96384715761888</v>
+        <v>14.96384720643676</v>
       </c>
       <c r="J191" s="2" t="n">
         <v>0.964531715016688</v>
@@ -10587,7 +10587,7 @@
         <v>-1</v>
       </c>
       <c r="N191" s="2" t="n">
-        <v>-0.0809309632925052</v>
+        <v>-0.0809309633645942</v>
       </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v/>
       </c>
       <c r="D192" s="2" t="n">
-        <v>213.7334492973866</v>
+        <v>213.7334492973844</v>
       </c>
       <c r="E192" s="2" t="n">
         <v>164</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="H192" s="2" t="n">
-        <v>40.41750675618885</v>
+        <v>40.41750673919419</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>13.03597076255722</v>
+        <v>13.03597082119285</v>
       </c>
       <c r="J192" s="2" t="n">
         <v>0.5939442380616455</v>
@@ -10640,7 +10640,7 @@
         <v>-1</v>
       </c>
       <c r="N192" s="2" t="n">
-        <v>-0.6272395732126141</v>
+        <v>-0.627239573573128</v>
       </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
@@ -10675,10 +10675,10 @@
         <v>0</v>
       </c>
       <c r="H193" s="2" t="n">
-        <v>40.39649190794629</v>
+        <v>40.39649178843747</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>21.52079984219306</v>
+        <v>21.52079987939417</v>
       </c>
       <c r="J193" s="2" t="n">
         <v>0.2978796823487169</v>
@@ -10693,7 +10693,7 @@
         <v>-1</v>
       </c>
       <c r="N193" s="2" t="n">
-        <v>0.1132021208045586</v>
+        <v>0.1132021208526307</v>
       </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
@@ -10731,7 +10731,7 @@
         <v>48.02799380209156</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>15.66489100983429</v>
+        <v>15.66489105131884</v>
       </c>
       <c r="J194" s="2" t="n">
         <v>0.5761783767673757</v>
@@ -10746,7 +10746,7 @@
         <v>-1</v>
       </c>
       <c r="N194" s="2" t="n">
-        <v>-0.0539445034730469</v>
+        <v>-0.0539445035090984</v>
       </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
@@ -10781,10 +10781,10 @@
         <v>0</v>
       </c>
       <c r="H195" s="2" t="n">
-        <v>40.58379855890672</v>
+        <v>40.5837984987164</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>14.59995438884363</v>
+        <v>14.59995440870226</v>
       </c>
       <c r="J195" s="2" t="n">
         <v>1.081083004155928</v>
@@ -10799,7 +10799,7 @@
         <v>-1</v>
       </c>
       <c r="N195" s="2" t="n">
-        <v>-0.0805861995248688</v>
+        <v>-0.08058619953688589</v>
       </c>
       <c r="O195" s="2" t="inlineStr">
         <is>
@@ -10834,10 +10834,10 @@
         <v>0</v>
       </c>
       <c r="H196" s="2" t="n">
-        <v>39.26865404545117</v>
+        <v>39.26865417115156</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>18.28109503499408</v>
+        <v>18.28109515561549</v>
       </c>
       <c r="J196" s="2" t="n">
         <v>0.5246800456781106</v>
@@ -10852,7 +10852,7 @@
         <v>-1</v>
       </c>
       <c r="N196" s="2" t="n">
-        <v>-0.1078084482847819</v>
+        <v>-0.1078084483568863</v>
       </c>
       <c r="O196" s="2" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v/>
       </c>
       <c r="D197" s="2" t="n">
-        <v>202.2235780303682</v>
+        <v>202.2235780303681</v>
       </c>
       <c r="E197" s="2" t="n">
         <v>32.65</v>
@@ -10887,10 +10887,10 @@
         <v>0</v>
       </c>
       <c r="H197" s="2" t="n">
-        <v>49.39760177979539</v>
+        <v>49.39760174702917</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>5.111754654206917</v>
+        <v>5.111754747989291</v>
       </c>
       <c r="J197" s="2" t="n">
         <v>0.5349881098118677</v>
@@ -10905,7 +10905,7 @@
         <v>-1</v>
       </c>
       <c r="N197" s="2" t="n">
-        <v>0.1223586402785915</v>
+        <v>0.1223586400863111</v>
       </c>
       <c r="O197" s="2" t="inlineStr">
         <is>
@@ -10940,10 +10940,10 @@
         <v>0</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>48.62437436347871</v>
+        <v>48.62437424373356</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>16.59348666545671</v>
+        <v>16.59348668664633</v>
       </c>
       <c r="J198" s="2" t="n">
         <v>0.9178751424102574</v>
@@ -10979,7 +10979,7 @@
         <v/>
       </c>
       <c r="D199" s="2" t="n">
-        <v>194.527940962778</v>
+        <v>194.5279409627783</v>
       </c>
       <c r="E199" s="2" t="n">
         <v>25.7</v>
@@ -10993,10 +10993,10 @@
         <v>0</v>
       </c>
       <c r="H199" s="2" t="n">
-        <v>45.27304668683079</v>
+        <v>45.27304654414295</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>15.04922595927195</v>
+        <v>15.04922597841911</v>
       </c>
       <c r="J199" s="2" t="n">
         <v>0.9828286531243546</v>
@@ -11011,7 +11011,7 @@
         <v>-1</v>
       </c>
       <c r="N199" s="2" t="n">
-        <v>0.0066598906229544</v>
+        <v>0.006659890695057</v>
       </c>
       <c r="O199" s="2" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v/>
       </c>
       <c r="D200" s="2" t="n">
-        <v>190.6053747804586</v>
+        <v>190.6053747804585</v>
       </c>
       <c r="E200" s="2" t="n">
         <v>33.45</v>
@@ -11046,10 +11046,10 @@
         <v>0</v>
       </c>
       <c r="H200" s="2" t="n">
-        <v>36.39470979245396</v>
+        <v>36.39470982328557</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>21.145275364126</v>
+        <v>21.14527523532427</v>
       </c>
       <c r="J200" s="2" t="n">
         <v>0.4543505400507371</v>
@@ -11064,7 +11064,7 @@
         <v>-1</v>
       </c>
       <c r="N200" s="2" t="n">
-        <v>0.039979315020926</v>
+        <v>0.0399793147325187</v>
       </c>
       <c r="O200" s="2" t="inlineStr">
         <is>
@@ -11099,10 +11099,10 @@
         <v>0</v>
       </c>
       <c r="H201" s="2" t="n">
-        <v>43.00242121708657</v>
+        <v>43.00242102876101</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>14.17751119253689</v>
+        <v>14.17751111742747</v>
       </c>
       <c r="J201" s="2" t="n">
         <v>0.1669001853132166</v>
@@ -11117,7 +11117,7 @@
         <v>-1</v>
       </c>
       <c r="N201" s="2" t="n">
-        <v>-0.08228500478750771</v>
+        <v>-0.0822850046433401</v>
       </c>
       <c r="O201" s="2" t="inlineStr">
         <is>
@@ -11152,10 +11152,10 @@
         <v>0</v>
       </c>
       <c r="H202" s="2" t="n">
-        <v>42.60846390890936</v>
+        <v>42.60846392731705</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>17.56838479655606</v>
+        <v>17.56838480451866</v>
       </c>
       <c r="J202" s="2" t="n">
         <v>0.4055846429090141</v>
@@ -11170,7 +11170,7 @@
         <v>-1</v>
       </c>
       <c r="N202" s="2" t="n">
-        <v>-0.1102478676225296</v>
+        <v>-0.1102478676105115</v>
       </c>
       <c r="O202" s="2" t="inlineStr">
         <is>
@@ -11205,10 +11205,10 @@
         <v>0</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>46.05505358428115</v>
+        <v>46.05505343591945</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>11.12271311712576</v>
+        <v>11.12271347786266</v>
       </c>
       <c r="J203" s="2" t="n">
         <v>0.2481570114490726</v>
@@ -11244,7 +11244,7 @@
         <v/>
       </c>
       <c r="D204" s="2" t="n">
-        <v>177.7715812946192</v>
+        <v>177.7715812946194</v>
       </c>
       <c r="E204" s="2" t="n">
         <v>18.8</v>
@@ -11258,10 +11258,10 @@
         <v>0</v>
       </c>
       <c r="H204" s="2" t="n">
-        <v>42.84218328677609</v>
+        <v>42.84218330754825</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>18.63661432342376</v>
+        <v>18.63661444176119</v>
       </c>
       <c r="J204" s="2" t="n">
         <v>0.2455985109624509</v>
@@ -11276,7 +11276,7 @@
         <v>-1</v>
       </c>
       <c r="N204" s="2" t="n">
-        <v>-0.0334495008472334</v>
+        <v>-0.0334495008953023</v>
       </c>
       <c r="O204" s="2" t="inlineStr">
         <is>
@@ -11311,10 +11311,10 @@
         <v>0</v>
       </c>
       <c r="H205" s="2" t="n">
-        <v>31.1771029423336</v>
+        <v>31.17710296249872</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>21.12058265361562</v>
+        <v>21.12058265896371</v>
       </c>
       <c r="J205" s="2" t="n">
         <v>0.8107972203318302</v>
@@ -11329,7 +11329,7 @@
         <v>-1</v>
       </c>
       <c r="N205" s="2" t="n">
-        <v>-0.0873546109225545</v>
+        <v>-0.08735461087448509</v>
       </c>
       <c r="O205" s="2" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v/>
       </c>
       <c r="D206" s="2" t="n">
-        <v>165.358647592958</v>
+        <v>165.3586475929572</v>
       </c>
       <c r="E206" s="2" t="n">
         <v>13.15</v>
@@ -11364,10 +11364,10 @@
         <v>0</v>
       </c>
       <c r="H206" s="2" t="n">
-        <v>36.66955776513534</v>
+        <v>36.66955792622006</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>11.3090852930451</v>
+        <v>11.30908528308296</v>
       </c>
       <c r="J206" s="2" t="n">
         <v>1.267335641597861</v>
@@ -11382,7 +11382,7 @@
         <v>-1</v>
       </c>
       <c r="N206" s="2" t="n">
-        <v>-0.0082410410567484</v>
+        <v>-0.008241041068765401</v>
       </c>
       <c r="O206" s="2" t="inlineStr">
         <is>
@@ -11417,10 +11417,10 @@
         <v>0</v>
       </c>
       <c r="H207" s="2" t="n">
-        <v>40.58186194552273</v>
+        <v>40.58186186336842</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>31.42273758426411</v>
+        <v>31.42273762828572</v>
       </c>
       <c r="J207" s="2" t="n">
         <v>0.3709338768050627</v>
@@ -11435,7 +11435,7 @@
         <v>-1</v>
       </c>
       <c r="N207" s="2" t="n">
-        <v>-0.0080136446447706</v>
+        <v>-0.008013644632752099</v>
       </c>
       <c r="O207" s="2" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v/>
       </c>
       <c r="D208" s="2" t="n">
-        <v>160.2971213718897</v>
+        <v>160.2971213718889</v>
       </c>
       <c r="E208" s="2" t="n">
         <v>39.4</v>
@@ -11470,10 +11470,10 @@
         <v>0</v>
       </c>
       <c r="H208" s="2" t="n">
-        <v>50.19470845752349</v>
+        <v>50.19470841426349</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>7.022069110464598</v>
+        <v>7.022069192669467</v>
       </c>
       <c r="J208" s="2" t="n">
         <v>0.1380663807213029</v>
@@ -11488,7 +11488,7 @@
         <v>-1</v>
       </c>
       <c r="N208" s="2" t="n">
-        <v>0.0697046196767148</v>
+        <v>0.06970461979688911</v>
       </c>
       <c r="O208" s="2" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>38.75471600911353</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>15.15165067004632</v>
+        <v>15.15165070798591</v>
       </c>
       <c r="J209" s="2" t="n">
         <v>0.3841001426028629</v>
@@ -11562,7 +11562,7 @@
         <v/>
       </c>
       <c r="D210" s="2" t="n">
-        <v>154.033425928486</v>
+        <v>154.0334259284855</v>
       </c>
       <c r="E210" s="2" t="n">
         <v>21.75</v>
@@ -11576,10 +11576,10 @@
         <v>0</v>
       </c>
       <c r="H210" s="2" t="n">
-        <v>43.1798472400305</v>
+        <v>43.17984716744778</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>18.63134023852804</v>
+        <v>18.63134032684395</v>
       </c>
       <c r="J210" s="2" t="n">
         <v>0.7838025558560217</v>
@@ -11594,7 +11594,7 @@
         <v>-1</v>
       </c>
       <c r="N210" s="2" t="n">
-        <v>0.0436801918436904</v>
+        <v>0.0436801918316744</v>
       </c>
       <c r="O210" s="2" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v/>
       </c>
       <c r="D211" s="2" t="n">
-        <v>153.4957513813672</v>
+        <v>153.4957513813678</v>
       </c>
       <c r="E211" s="2" t="n">
         <v>8</v>
@@ -11629,7 +11629,7 @@
         <v>0</v>
       </c>
       <c r="H211" s="2" t="n">
-        <v>51.09486708282223</v>
+        <v>51.09486707792627</v>
       </c>
       <c r="I211" s="2" t="n">
         <v>4.802568958032945</v>
@@ -11647,7 +11647,7 @@
         <v>-1</v>
       </c>
       <c r="N211" s="2" t="n">
-        <v>-0.009146038436912999</v>
+        <v>-0.009146038400861299</v>
       </c>
       <c r="O211" s="2" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>40.41334366353672</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>15.59398222647041</v>
+        <v>15.59398216031527</v>
       </c>
       <c r="J212" s="2" t="n">
         <v>0.6672651983990608</v>
@@ -11700,7 +11700,7 @@
         <v>-1</v>
       </c>
       <c r="N212" s="2" t="n">
-        <v>-0.0206512438421095</v>
+        <v>-0.0206512439382446</v>
       </c>
       <c r="O212" s="2" t="inlineStr">
         <is>
@@ -11735,10 +11735,10 @@
         <v>0</v>
       </c>
       <c r="H213" s="2" t="n">
-        <v>41.9838073805468</v>
+        <v>41.98380734268876</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>13.68865923013519</v>
+        <v>13.68865921380188</v>
       </c>
       <c r="J213" s="2" t="n">
         <v>0.6917690167449165</v>
@@ -11753,7 +11753,7 @@
         <v>-1</v>
       </c>
       <c r="N213" s="2" t="n">
-        <v>-0.0030526252525276</v>
+        <v>-0.003052625264545</v>
       </c>
       <c r="O213" s="2" t="inlineStr">
         <is>
@@ -11763,21 +11763,21 @@
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>2701</v>
+        <v>2836</v>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>萬企</t>
+          <t>高雄銀</t>
         </is>
       </c>
       <c r="C214" s="2" t="n">
         <v/>
       </c>
       <c r="D214" s="2" t="n">
-        <v>143.7666355958059</v>
+        <v>148.0671070531555</v>
       </c>
       <c r="E214" s="2" t="n">
-        <v>10.3</v>
+        <v>12.05</v>
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
@@ -11788,13 +11788,13 @@
         <v>0</v>
       </c>
       <c r="H214" s="2" t="n">
-        <v>44.65511657980243</v>
+        <v>46.2627383206448</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>14.22684826127909</v>
+        <v>13.19919864596346</v>
       </c>
       <c r="J214" s="2" t="n">
-        <v>0.7707217702925507</v>
+        <v>0.7025406475775822</v>
       </c>
       <c r="K214" s="2" t="n">
         <v>0</v>
@@ -11806,31 +11806,31 @@
         <v>-1</v>
       </c>
       <c r="N214" s="2" t="n">
-        <v>0.0107015872013494</v>
+        <v>-0.0219324018578159</v>
       </c>
       <c r="O214" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>2524</v>
+        <v>2701</v>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>京城</t>
+          <t>萬企</t>
         </is>
       </c>
       <c r="C215" s="2" t="n">
         <v/>
       </c>
       <c r="D215" s="2" t="n">
-        <v>141.8455213798514</v>
+        <v>143.7666355958059</v>
       </c>
       <c r="E215" s="2" t="n">
-        <v>33.65</v>
+        <v>10.3</v>
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
@@ -11841,13 +11841,13 @@
         <v>0</v>
       </c>
       <c r="H215" s="2" t="n">
-        <v>43.07107228611675</v>
+        <v>44.65511652196243</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>9.703643375410746</v>
+        <v>14.22684819020028</v>
       </c>
       <c r="J215" s="2" t="n">
-        <v>0.3215971391065982</v>
+        <v>0.7707217702925507</v>
       </c>
       <c r="K215" s="2" t="n">
         <v>0</v>
@@ -11859,7 +11859,7 @@
         <v>-1</v>
       </c>
       <c r="N215" s="2" t="n">
-        <v>-0.1238853658336985</v>
+        <v>0.0107015872013494</v>
       </c>
       <c r="O215" s="2" t="inlineStr">
         <is>
@@ -11869,21 +11869,21 @@
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>2505</v>
+        <v>2524</v>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>國揚</t>
+          <t>京城</t>
         </is>
       </c>
       <c r="C216" s="2" t="n">
         <v/>
       </c>
       <c r="D216" s="2" t="n">
-        <v>130.5535784887266</v>
+        <v>141.8455213798518</v>
       </c>
       <c r="E216" s="2" t="n">
-        <v>17</v>
+        <v>33.65</v>
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
@@ -11894,16 +11894,16 @@
         <v>0</v>
       </c>
       <c r="H216" s="2" t="n">
-        <v>43.04115082833285</v>
+        <v>43.07107218627289</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>16.62649954606928</v>
+        <v>9.703643458853463</v>
       </c>
       <c r="J216" s="2" t="n">
-        <v>0.2657428434190147</v>
+        <v>0.3215971391065982</v>
       </c>
       <c r="K216" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L216" s="2" t="n">
         <v>0</v>
@@ -11912,7 +11912,7 @@
         <v>-1</v>
       </c>
       <c r="N216" s="2" t="n">
-        <v>0.0149741190047486</v>
+        <v>-0.1238853656534402</v>
       </c>
       <c r="O216" s="2" t="inlineStr">
         <is>
@@ -11922,21 +11922,21 @@
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>2630</v>
+        <v>2505</v>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>亞航</t>
+          <t>國揚</t>
         </is>
       </c>
       <c r="C217" s="2" t="n">
         <v/>
       </c>
       <c r="D217" s="2" t="n">
-        <v>125.658133918206</v>
+        <v>130.5535784887266</v>
       </c>
       <c r="E217" s="2" t="n">
-        <v>45.2</v>
+        <v>17</v>
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
@@ -11947,16 +11947,16 @@
         <v>0</v>
       </c>
       <c r="H217" s="2" t="n">
-        <v>33.49943309659074</v>
+        <v>43.04115049561384</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>10.74378699687276</v>
+        <v>16.62649958742404</v>
       </c>
       <c r="J217" s="2" t="n">
-        <v>0.7121161540160343</v>
+        <v>0.2657428434190147</v>
       </c>
       <c r="K217" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L217" s="2" t="n">
         <v>0</v>
@@ -11965,7 +11965,7 @@
         <v>-1</v>
       </c>
       <c r="N217" s="2" t="n">
-        <v>-0.0628103614096428</v>
+        <v>0.014974119028783</v>
       </c>
       <c r="O217" s="2" t="inlineStr">
         <is>
@@ -11975,21 +11975,21 @@
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>2903</v>
+        <v>2630</v>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>遠百</t>
+          <t>亞航</t>
         </is>
       </c>
       <c r="C218" s="2" t="n">
         <v/>
       </c>
       <c r="D218" s="2" t="n">
-        <v>108.5033742401454</v>
+        <v>125.6581339182079</v>
       </c>
       <c r="E218" s="2" t="n">
-        <v>22.15</v>
+        <v>45.2</v>
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
@@ -12000,13 +12000,13 @@
         <v>0</v>
       </c>
       <c r="H218" s="2" t="n">
-        <v>51.43830964689423</v>
+        <v>33.49943237805158</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>13.40893994886778</v>
+        <v>10.74378702063726</v>
       </c>
       <c r="J218" s="2" t="n">
-        <v>1.097071629435313</v>
+        <v>0.7121161540160343</v>
       </c>
       <c r="K218" s="2" t="n">
         <v>2</v>
@@ -12018,7 +12018,7 @@
         <v>-1</v>
       </c>
       <c r="N218" s="2" t="n">
-        <v>-0.0077973753364535</v>
+        <v>-0.06281036092895539</v>
       </c>
       <c r="O218" s="2" t="inlineStr">
         <is>
@@ -12028,21 +12028,21 @@
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>2836</v>
+        <v>2903</v>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>高雄銀</t>
+          <t>遠百</t>
         </is>
       </c>
       <c r="C219" s="2" t="n">
         <v/>
       </c>
       <c r="D219" s="2" t="n">
-        <v>88.06710705315542</v>
+        <v>108.5033742401454</v>
       </c>
       <c r="E219" s="2" t="n">
-        <v>12.05</v>
+        <v>22.15</v>
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
@@ -12053,16 +12053,16 @@
         <v>0</v>
       </c>
       <c r="H219" s="2" t="n">
-        <v>46.26273824683504</v>
+        <v>51.43830960557761</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>13.1991985832413</v>
+        <v>13.40893993819791</v>
       </c>
       <c r="J219" s="2" t="n">
-        <v>0.7025406475775822</v>
+        <v>1.097071629435313</v>
       </c>
       <c r="K219" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L219" s="2" t="n">
         <v>0</v>
@@ -12071,7 +12071,7 @@
         <v>-1</v>
       </c>
       <c r="N219" s="2" t="n">
-        <v>-0.0219324018457982</v>
+        <v>-0.0077973753364535</v>
       </c>
       <c r="O219" s="2" t="inlineStr">
         <is>
@@ -12106,10 +12106,10 @@
         <v>0</v>
       </c>
       <c r="H220" s="2" t="n">
-        <v>39.85647314173026</v>
+        <v>39.85647285502302</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>16.4886263725902</v>
+        <v>16.48862656662084</v>
       </c>
       <c r="J220" s="2" t="n">
         <v>0.8724520171968554</v>
@@ -12124,7 +12124,7 @@
         <v>-1</v>
       </c>
       <c r="N220" s="2" t="n">
-        <v>-0.0566975392496068</v>
+        <v>-0.0566975391053961</v>
       </c>
       <c r="O220" s="2" t="inlineStr">
         <is>
